--- a/data/sample_inputs.xlsx
+++ b/data/sample_inputs.xlsx
@@ -23,6 +23,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plant_Hours" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spot" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer_Types" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer_Routes" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,10 +434,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -632,16 +634,40 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Transfer_Types</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>What can be moved between sites (milk, cream, permeate) and its kg/kL composition range</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Transfer_Routes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Allowed site-to-site transfers, cost $/kL and weekly limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>All data in this workbook is made up for demonstration purposes.</t>
         </is>
@@ -25285,6 +25311,741 @@
       </c>
       <c r="C53" t="n">
         <v>733</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>transfer_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>source_stream</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>dest_stream</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>whole_milk</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fat_min_kg_per_kL</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fat_max_kg_per_kL</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>protein_min_kg_per_kL</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>protein_max_kg_per_kL</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>la_min_kg_per_kL</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>la_max_kg_per_kL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MILK</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Whole milk (standardised within a normal milk range)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MILK</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MILK</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G2" t="n">
+        <v>47</v>
+      </c>
+      <c r="H2" t="n">
+        <v>31</v>
+      </c>
+      <c r="I2" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2" t="n">
+        <v>55</v>
+      </c>
+      <c r="K2" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CREAM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cream ~40% fat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MILK</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MILK</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>380</v>
+      </c>
+      <c r="G3" t="n">
+        <v>420</v>
+      </c>
+      <c r="H3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I3" t="n">
+        <v>22</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K3" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PERMEATE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UF permeate, RO-concentrated to ~18% solids</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MILK</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MILK</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>170</v>
+      </c>
+      <c r="K4" t="n">
+        <v>190</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>transfer_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>from_factory</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>to_factory</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>distance_km</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>cost_per_kL</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>max_kL_per_week</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MILK</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BOR</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>310</v>
+      </c>
+      <c r="E2" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MILK</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BOR</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>310</v>
+      </c>
+      <c r="E3" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MILK</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>540</v>
+      </c>
+      <c r="E4" t="n">
+        <v>81</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MILK</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>540</v>
+      </c>
+      <c r="E5" t="n">
+        <v>81</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MILK</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BOR</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>820</v>
+      </c>
+      <c r="E6" t="n">
+        <v>123</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MILK</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BOR</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>820</v>
+      </c>
+      <c r="E7" t="n">
+        <v>123</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CREAM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BOR</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>310</v>
+      </c>
+      <c r="E8" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CREAM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BOR</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>310</v>
+      </c>
+      <c r="E9" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CREAM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>540</v>
+      </c>
+      <c r="E10" t="n">
+        <v>81</v>
+      </c>
+      <c r="F10" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CREAM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>540</v>
+      </c>
+      <c r="E11" t="n">
+        <v>81</v>
+      </c>
+      <c r="F11" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CREAM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BOR</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>820</v>
+      </c>
+      <c r="E12" t="n">
+        <v>123</v>
+      </c>
+      <c r="F12" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CREAM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BOR</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>820</v>
+      </c>
+      <c r="E13" t="n">
+        <v>123</v>
+      </c>
+      <c r="F13" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PERMEATE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BOR</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>310</v>
+      </c>
+      <c r="E14" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PERMEATE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BOR</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>310</v>
+      </c>
+      <c r="E15" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PERMEATE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>540</v>
+      </c>
+      <c r="E16" t="n">
+        <v>81</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PERMEATE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>540</v>
+      </c>
+      <c r="E17" t="n">
+        <v>81</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PERMEATE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BOR</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>820</v>
+      </c>
+      <c r="E18" t="n">
+        <v>123</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PERMEATE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CYG</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BOR</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>820</v>
+      </c>
+      <c r="E19" t="n">
+        <v>123</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/data/sample_inputs.xlsx
+++ b/data/sample_inputs.xlsx
@@ -25328,7 +25328,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="73" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -25448,7 +25448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cream ~40% fat</t>
+          <t>Cream 40% fat (~396 kg fat/kL at 0.99 kg/L)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -25465,10 +25465,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="G3" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="H3" t="n">
         <v>18</v>
@@ -25491,7 +25491,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UF permeate, RO-concentrated to ~18% solids</t>
+          <t>UF permeate concentrated to 18% solids (~193 kg solids/kL at 1.07 kg/L)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -25520,7 +25520,7 @@
         <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="K4" t="n">
         <v>190</v>

--- a/data/sample_inputs.xlsx
+++ b/data/sample_inputs.xlsx
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="3">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>1.792</v>
       </c>
     </row>
     <row r="4">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>1.792</v>
       </c>
     </row>
     <row r="5">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="6">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="7">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.5</v>
+        <v>0.896</v>
       </c>
     </row>
     <row r="8">
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>2.048</v>
       </c>
     </row>
     <row r="9">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>2.048</v>
       </c>
     </row>
     <row r="10">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>0.512</v>
       </c>
     </row>
     <row r="11">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="12">
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>3.072</v>
       </c>
     </row>
     <row r="13">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>3.072</v>
       </c>
     </row>
     <row r="14">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>1.792</v>
       </c>
     </row>
     <row r="15">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>2.048</v>
       </c>
     </row>
     <row r="16">
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>2.048</v>
       </c>
     </row>
     <row r="17">
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="18">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="19">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="20">
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.5</v>
+        <v>0.384</v>
       </c>
     </row>
     <row r="21">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="22">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="23">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>2.048</v>
       </c>
     </row>
     <row r="24">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>1.536</v>
       </c>
     </row>
     <row r="25">
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.2</v>
+        <v>0.3072</v>
       </c>
     </row>
     <row r="26">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.8</v>
+        <v>0.2048</v>
       </c>
     </row>
     <row r="27">
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.5</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="28">
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>0.768</v>
       </c>
     </row>
   </sheetData>
@@ -14373,7 +14373,7 @@
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="107">
@@ -14392,7 +14392,7 @@
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108">
@@ -14411,7 +14411,7 @@
         <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109">
@@ -14430,7 +14430,7 @@
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="110">
@@ -14449,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="111">
@@ -14468,7 +14468,7 @@
         <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="112">
@@ -14487,7 +14487,7 @@
         <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="113">
@@ -14506,7 +14506,7 @@
         <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="114">
@@ -14525,7 +14525,7 @@
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="115">
@@ -14544,7 +14544,7 @@
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="116">
@@ -14563,7 +14563,7 @@
         <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="117">
@@ -14582,7 +14582,7 @@
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="118">
@@ -14601,7 +14601,7 @@
         <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="119">
@@ -14620,7 +14620,7 @@
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="120">
@@ -14639,7 +14639,7 @@
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="121">
@@ -14658,7 +14658,7 @@
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="122">
@@ -14677,7 +14677,7 @@
         <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="123">
@@ -14696,7 +14696,7 @@
         <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="124">
@@ -14715,7 +14715,7 @@
         <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="125">
@@ -14734,7 +14734,7 @@
         <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="126">
@@ -14753,7 +14753,7 @@
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="127">
@@ -14772,7 +14772,7 @@
         <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="128">
@@ -14791,7 +14791,7 @@
         <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="129">
@@ -14810,7 +14810,7 @@
         <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="130">
@@ -14829,7 +14829,7 @@
         <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131">
@@ -14848,7 +14848,7 @@
         <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="132">
@@ -14867,7 +14867,7 @@
         <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="133">
@@ -14886,7 +14886,7 @@
         <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134">
@@ -14905,7 +14905,7 @@
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="135">
@@ -14924,7 +14924,7 @@
         <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="136">
@@ -14943,7 +14943,7 @@
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="137">
@@ -14962,7 +14962,7 @@
         <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="138">
@@ -14981,7 +14981,7 @@
         <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139">
@@ -15000,7 +15000,7 @@
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="140">
@@ -15019,7 +15019,7 @@
         <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="141">
@@ -15038,7 +15038,7 @@
         <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="142">
@@ -15057,7 +15057,7 @@
         <v>0</v>
       </c>
       <c r="E142" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="143">
@@ -15076,7 +15076,7 @@
         <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="144">
@@ -15095,7 +15095,7 @@
         <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="145">
@@ -15114,7 +15114,7 @@
         <v>0</v>
       </c>
       <c r="E145" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="146">
@@ -15133,7 +15133,7 @@
         <v>0</v>
       </c>
       <c r="E146" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="147">
@@ -15152,7 +15152,7 @@
         <v>0</v>
       </c>
       <c r="E147" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="148">
@@ -15171,7 +15171,7 @@
         <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="149">
@@ -15190,7 +15190,7 @@
         <v>0</v>
       </c>
       <c r="E149" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="150">
@@ -15209,7 +15209,7 @@
         <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="151">
@@ -15228,7 +15228,7 @@
         <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="152">
@@ -15247,7 +15247,7 @@
         <v>0</v>
       </c>
       <c r="E152" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="153">
@@ -15266,7 +15266,7 @@
         <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="154">
@@ -15285,7 +15285,7 @@
         <v>0</v>
       </c>
       <c r="E154" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="155">
@@ -15304,7 +15304,7 @@
         <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="156">
@@ -15323,7 +15323,7 @@
         <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="157">
@@ -15342,7 +15342,7 @@
         <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="158">
@@ -18010,10 +18010,10 @@
         <v>13000</v>
       </c>
       <c r="D314" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E314" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="315">
@@ -18029,10 +18029,10 @@
         <v>13000</v>
       </c>
       <c r="D315" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E315" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="316">
@@ -18048,10 +18048,10 @@
         <v>13000</v>
       </c>
       <c r="D316" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E316" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="317">
@@ -18067,10 +18067,10 @@
         <v>13000</v>
       </c>
       <c r="D317" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E317" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="318">
@@ -18086,10 +18086,10 @@
         <v>13000</v>
       </c>
       <c r="D318" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E318" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="319">
@@ -18105,10 +18105,10 @@
         <v>13000</v>
       </c>
       <c r="D319" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E319" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="320">
@@ -18124,10 +18124,10 @@
         <v>13000</v>
       </c>
       <c r="D320" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E320" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="321">
@@ -18143,10 +18143,10 @@
         <v>13000</v>
       </c>
       <c r="D321" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E321" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="322">
@@ -18162,10 +18162,10 @@
         <v>13000</v>
       </c>
       <c r="D322" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E322" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="323">
@@ -18181,10 +18181,10 @@
         <v>13000</v>
       </c>
       <c r="D323" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E323" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="324">
@@ -18200,10 +18200,10 @@
         <v>13000</v>
       </c>
       <c r="D324" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E324" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="325">
@@ -18219,10 +18219,10 @@
         <v>13000</v>
       </c>
       <c r="D325" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E325" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="326">
@@ -18238,10 +18238,10 @@
         <v>13000</v>
       </c>
       <c r="D326" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E326" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="327">
@@ -18257,10 +18257,10 @@
         <v>13000</v>
       </c>
       <c r="D327" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E327" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="328">
@@ -18276,10 +18276,10 @@
         <v>13000</v>
       </c>
       <c r="D328" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E328" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="329">
@@ -18295,10 +18295,10 @@
         <v>13000</v>
       </c>
       <c r="D329" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E329" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="330">
@@ -18314,10 +18314,10 @@
         <v>13000</v>
       </c>
       <c r="D330" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E330" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="331">
@@ -18333,10 +18333,10 @@
         <v>13000</v>
       </c>
       <c r="D331" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E331" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="332">
@@ -18352,10 +18352,10 @@
         <v>13000</v>
       </c>
       <c r="D332" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E332" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="333">
@@ -18371,10 +18371,10 @@
         <v>13000</v>
       </c>
       <c r="D333" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E333" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="334">
@@ -18390,10 +18390,10 @@
         <v>13000</v>
       </c>
       <c r="D334" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E334" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="335">
@@ -18409,10 +18409,10 @@
         <v>13000</v>
       </c>
       <c r="D335" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E335" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="336">
@@ -18428,10 +18428,10 @@
         <v>13000</v>
       </c>
       <c r="D336" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E336" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="337">
@@ -18447,10 +18447,10 @@
         <v>13000</v>
       </c>
       <c r="D337" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E337" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="338">
@@ -18466,10 +18466,10 @@
         <v>13000</v>
       </c>
       <c r="D338" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E338" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="339">
@@ -18485,10 +18485,10 @@
         <v>13000</v>
       </c>
       <c r="D339" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E339" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="340">
@@ -18504,10 +18504,10 @@
         <v>13000</v>
       </c>
       <c r="D340" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E340" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="341">
@@ -18523,10 +18523,10 @@
         <v>13000</v>
       </c>
       <c r="D341" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E341" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="342">
@@ -18542,10 +18542,10 @@
         <v>13000</v>
       </c>
       <c r="D342" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E342" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="343">
@@ -18561,10 +18561,10 @@
         <v>13000</v>
       </c>
       <c r="D343" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E343" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="344">
@@ -18580,10 +18580,10 @@
         <v>13000</v>
       </c>
       <c r="D344" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E344" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="345">
@@ -18599,10 +18599,10 @@
         <v>13000</v>
       </c>
       <c r="D345" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E345" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="346">
@@ -18618,10 +18618,10 @@
         <v>13000</v>
       </c>
       <c r="D346" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E346" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="347">
@@ -18637,10 +18637,10 @@
         <v>13000</v>
       </c>
       <c r="D347" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E347" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="348">
@@ -18656,10 +18656,10 @@
         <v>13000</v>
       </c>
       <c r="D348" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E348" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="349">
@@ -18675,10 +18675,10 @@
         <v>13000</v>
       </c>
       <c r="D349" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E349" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="350">
@@ -18694,10 +18694,10 @@
         <v>13000</v>
       </c>
       <c r="D350" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E350" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="351">
@@ -18713,10 +18713,10 @@
         <v>13000</v>
       </c>
       <c r="D351" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E351" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="352">
@@ -18732,10 +18732,10 @@
         <v>13000</v>
       </c>
       <c r="D352" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E352" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="353">
@@ -18751,10 +18751,10 @@
         <v>13000</v>
       </c>
       <c r="D353" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E353" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="354">
@@ -18770,10 +18770,10 @@
         <v>13000</v>
       </c>
       <c r="D354" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E354" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="355">
@@ -18789,10 +18789,10 @@
         <v>13000</v>
       </c>
       <c r="D355" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E355" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="356">
@@ -18808,10 +18808,10 @@
         <v>13000</v>
       </c>
       <c r="D356" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E356" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="357">
@@ -18827,10 +18827,10 @@
         <v>13000</v>
       </c>
       <c r="D357" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E357" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="358">
@@ -18846,10 +18846,10 @@
         <v>13000</v>
       </c>
       <c r="D358" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E358" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="359">
@@ -18865,10 +18865,10 @@
         <v>13000</v>
       </c>
       <c r="D359" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E359" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="360">
@@ -18884,10 +18884,10 @@
         <v>13000</v>
       </c>
       <c r="D360" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E360" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="361">
@@ -18903,10 +18903,10 @@
         <v>13000</v>
       </c>
       <c r="D361" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E361" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="362">
@@ -18922,10 +18922,10 @@
         <v>13000</v>
       </c>
       <c r="D362" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E362" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="363">
@@ -18941,10 +18941,10 @@
         <v>13000</v>
       </c>
       <c r="D363" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E363" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="364">
@@ -18960,10 +18960,10 @@
         <v>13000</v>
       </c>
       <c r="D364" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E364" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="365">
@@ -18979,10 +18979,10 @@
         <v>13000</v>
       </c>
       <c r="D365" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E365" t="n">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="366">
@@ -20766,10 +20766,10 @@
         <v>8200</v>
       </c>
       <c r="D470" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E470" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="471">
@@ -20785,10 +20785,10 @@
         <v>8200</v>
       </c>
       <c r="D471" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E471" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="472">
@@ -20804,10 +20804,10 @@
         <v>8200</v>
       </c>
       <c r="D472" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E472" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="473">
@@ -20823,10 +20823,10 @@
         <v>8200</v>
       </c>
       <c r="D473" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E473" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="474">
@@ -20842,10 +20842,10 @@
         <v>8200</v>
       </c>
       <c r="D474" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E474" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="475">
@@ -20861,10 +20861,10 @@
         <v>8200</v>
       </c>
       <c r="D475" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E475" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="476">
@@ -20880,10 +20880,10 @@
         <v>8200</v>
       </c>
       <c r="D476" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E476" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="477">
@@ -20899,10 +20899,10 @@
         <v>8200</v>
       </c>
       <c r="D477" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E477" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="478">
@@ -20918,10 +20918,10 @@
         <v>8200</v>
       </c>
       <c r="D478" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E478" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="479">
@@ -20937,10 +20937,10 @@
         <v>8200</v>
       </c>
       <c r="D479" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E479" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="480">
@@ -20956,10 +20956,10 @@
         <v>8200</v>
       </c>
       <c r="D480" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E480" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="481">
@@ -20975,10 +20975,10 @@
         <v>8200</v>
       </c>
       <c r="D481" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E481" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="482">
@@ -20994,10 +20994,10 @@
         <v>8200</v>
       </c>
       <c r="D482" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E482" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="483">
@@ -21013,10 +21013,10 @@
         <v>8200</v>
       </c>
       <c r="D483" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E483" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="484">
@@ -21032,10 +21032,10 @@
         <v>8200</v>
       </c>
       <c r="D484" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E484" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="485">
@@ -21051,10 +21051,10 @@
         <v>8200</v>
       </c>
       <c r="D485" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E485" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="486">
@@ -21070,10 +21070,10 @@
         <v>8200</v>
       </c>
       <c r="D486" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E486" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="487">
@@ -21089,10 +21089,10 @@
         <v>8200</v>
       </c>
       <c r="D487" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E487" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="488">
@@ -21108,10 +21108,10 @@
         <v>8200</v>
       </c>
       <c r="D488" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E488" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="489">
@@ -21127,10 +21127,10 @@
         <v>8200</v>
       </c>
       <c r="D489" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E489" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="490">
@@ -21146,10 +21146,10 @@
         <v>8200</v>
       </c>
       <c r="D490" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E490" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="491">
@@ -21165,10 +21165,10 @@
         <v>8200</v>
       </c>
       <c r="D491" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E491" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="492">
@@ -21184,10 +21184,10 @@
         <v>8200</v>
       </c>
       <c r="D492" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E492" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="493">
@@ -21203,10 +21203,10 @@
         <v>8200</v>
       </c>
       <c r="D493" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E493" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="494">
@@ -21222,10 +21222,10 @@
         <v>8200</v>
       </c>
       <c r="D494" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E494" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="495">
@@ -21241,10 +21241,10 @@
         <v>8200</v>
       </c>
       <c r="D495" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E495" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="496">
@@ -21260,10 +21260,10 @@
         <v>8200</v>
       </c>
       <c r="D496" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E496" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="497">
@@ -21279,10 +21279,10 @@
         <v>8200</v>
       </c>
       <c r="D497" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E497" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="498">
@@ -21298,10 +21298,10 @@
         <v>8200</v>
       </c>
       <c r="D498" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E498" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="499">
@@ -21317,10 +21317,10 @@
         <v>8200</v>
       </c>
       <c r="D499" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E499" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="500">
@@ -21336,10 +21336,10 @@
         <v>8200</v>
       </c>
       <c r="D500" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E500" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="501">
@@ -21355,10 +21355,10 @@
         <v>8200</v>
       </c>
       <c r="D501" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E501" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="502">
@@ -21374,10 +21374,10 @@
         <v>8200</v>
       </c>
       <c r="D502" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E502" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="503">
@@ -21393,10 +21393,10 @@
         <v>8200</v>
       </c>
       <c r="D503" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E503" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="504">
@@ -21412,10 +21412,10 @@
         <v>8200</v>
       </c>
       <c r="D504" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E504" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="505">
@@ -21431,10 +21431,10 @@
         <v>8200</v>
       </c>
       <c r="D505" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E505" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="506">
@@ -21450,10 +21450,10 @@
         <v>8200</v>
       </c>
       <c r="D506" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E506" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="507">
@@ -21469,10 +21469,10 @@
         <v>8200</v>
       </c>
       <c r="D507" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E507" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="508">
@@ -21488,10 +21488,10 @@
         <v>8200</v>
       </c>
       <c r="D508" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E508" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="509">
@@ -21507,10 +21507,10 @@
         <v>8200</v>
       </c>
       <c r="D509" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E509" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="510">
@@ -21526,10 +21526,10 @@
         <v>8200</v>
       </c>
       <c r="D510" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E510" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="511">
@@ -21545,10 +21545,10 @@
         <v>8200</v>
       </c>
       <c r="D511" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E511" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="512">
@@ -21564,10 +21564,10 @@
         <v>8200</v>
       </c>
       <c r="D512" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E512" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="513">
@@ -21583,10 +21583,10 @@
         <v>8200</v>
       </c>
       <c r="D513" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E513" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="514">
@@ -21602,10 +21602,10 @@
         <v>8200</v>
       </c>
       <c r="D514" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E514" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="515">
@@ -21621,10 +21621,10 @@
         <v>8200</v>
       </c>
       <c r="D515" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E515" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="516">
@@ -21640,10 +21640,10 @@
         <v>8200</v>
       </c>
       <c r="D516" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E516" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="517">
@@ -21659,10 +21659,10 @@
         <v>8200</v>
       </c>
       <c r="D517" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E517" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="518">
@@ -21678,10 +21678,10 @@
         <v>8200</v>
       </c>
       <c r="D518" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E518" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="519">
@@ -21697,10 +21697,10 @@
         <v>8200</v>
       </c>
       <c r="D519" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E519" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="520">
@@ -21716,10 +21716,10 @@
         <v>8200</v>
       </c>
       <c r="D520" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E520" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="521">
@@ -21735,10 +21735,10 @@
         <v>8200</v>
       </c>
       <c r="D521" t="n">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="E521" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
     </row>
     <row r="522">
@@ -21754,10 +21754,10 @@
         <v>11000</v>
       </c>
       <c r="D522" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E522" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="523">
@@ -21773,10 +21773,10 @@
         <v>11000</v>
       </c>
       <c r="D523" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E523" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="524">
@@ -21792,10 +21792,10 @@
         <v>11000</v>
       </c>
       <c r="D524" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E524" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="525">
@@ -21811,10 +21811,10 @@
         <v>11000</v>
       </c>
       <c r="D525" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E525" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="526">
@@ -21830,10 +21830,10 @@
         <v>11000</v>
       </c>
       <c r="D526" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E526" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="527">
@@ -21849,10 +21849,10 @@
         <v>11000</v>
       </c>
       <c r="D527" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E527" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="528">
@@ -21868,10 +21868,10 @@
         <v>11000</v>
       </c>
       <c r="D528" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E528" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="529">
@@ -21887,10 +21887,10 @@
         <v>11000</v>
       </c>
       <c r="D529" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E529" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="530">
@@ -21906,10 +21906,10 @@
         <v>11000</v>
       </c>
       <c r="D530" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E530" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="531">
@@ -21925,10 +21925,10 @@
         <v>11000</v>
       </c>
       <c r="D531" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E531" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="532">
@@ -21944,10 +21944,10 @@
         <v>11000</v>
       </c>
       <c r="D532" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E532" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="533">
@@ -21963,10 +21963,10 @@
         <v>11000</v>
       </c>
       <c r="D533" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E533" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="534">
@@ -21982,10 +21982,10 @@
         <v>11000</v>
       </c>
       <c r="D534" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E534" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="535">
@@ -22001,10 +22001,10 @@
         <v>11000</v>
       </c>
       <c r="D535" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E535" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="536">
@@ -22020,10 +22020,10 @@
         <v>11000</v>
       </c>
       <c r="D536" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E536" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="537">
@@ -22039,10 +22039,10 @@
         <v>11000</v>
       </c>
       <c r="D537" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E537" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="538">
@@ -22058,10 +22058,10 @@
         <v>11000</v>
       </c>
       <c r="D538" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E538" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="539">
@@ -22077,10 +22077,10 @@
         <v>11000</v>
       </c>
       <c r="D539" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E539" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="540">
@@ -22096,10 +22096,10 @@
         <v>11000</v>
       </c>
       <c r="D540" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E540" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="541">
@@ -22115,10 +22115,10 @@
         <v>11000</v>
       </c>
       <c r="D541" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E541" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="542">
@@ -22134,10 +22134,10 @@
         <v>11000</v>
       </c>
       <c r="D542" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E542" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="543">
@@ -22153,10 +22153,10 @@
         <v>11000</v>
       </c>
       <c r="D543" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E543" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="544">
@@ -22172,10 +22172,10 @@
         <v>11000</v>
       </c>
       <c r="D544" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E544" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="545">
@@ -22191,10 +22191,10 @@
         <v>11000</v>
       </c>
       <c r="D545" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E545" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="546">
@@ -22210,10 +22210,10 @@
         <v>11000</v>
       </c>
       <c r="D546" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E546" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="547">
@@ -22229,10 +22229,10 @@
         <v>11000</v>
       </c>
       <c r="D547" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E547" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="548">
@@ -22248,10 +22248,10 @@
         <v>11000</v>
       </c>
       <c r="D548" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E548" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="549">
@@ -22267,10 +22267,10 @@
         <v>11000</v>
       </c>
       <c r="D549" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E549" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="550">
@@ -22286,10 +22286,10 @@
         <v>11000</v>
       </c>
       <c r="D550" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E550" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="551">
@@ -22305,10 +22305,10 @@
         <v>11000</v>
       </c>
       <c r="D551" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E551" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="552">
@@ -22324,10 +22324,10 @@
         <v>11000</v>
       </c>
       <c r="D552" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E552" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="553">
@@ -22343,10 +22343,10 @@
         <v>11000</v>
       </c>
       <c r="D553" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E553" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="554">
@@ -22362,10 +22362,10 @@
         <v>11000</v>
       </c>
       <c r="D554" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E554" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="555">
@@ -22381,10 +22381,10 @@
         <v>11000</v>
       </c>
       <c r="D555" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E555" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="556">
@@ -22400,10 +22400,10 @@
         <v>11000</v>
       </c>
       <c r="D556" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E556" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="557">
@@ -22419,10 +22419,10 @@
         <v>11000</v>
       </c>
       <c r="D557" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E557" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="558">
@@ -22438,10 +22438,10 @@
         <v>11000</v>
       </c>
       <c r="D558" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E558" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="559">
@@ -22457,10 +22457,10 @@
         <v>11000</v>
       </c>
       <c r="D559" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E559" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="560">
@@ -22476,10 +22476,10 @@
         <v>11000</v>
       </c>
       <c r="D560" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E560" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="561">
@@ -22495,10 +22495,10 @@
         <v>11000</v>
       </c>
       <c r="D561" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E561" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="562">
@@ -22514,10 +22514,10 @@
         <v>11000</v>
       </c>
       <c r="D562" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E562" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="563">
@@ -22533,10 +22533,10 @@
         <v>11000</v>
       </c>
       <c r="D563" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E563" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="564">
@@ -22552,10 +22552,10 @@
         <v>11000</v>
       </c>
       <c r="D564" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E564" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="565">
@@ -22571,10 +22571,10 @@
         <v>11000</v>
       </c>
       <c r="D565" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E565" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="566">
@@ -22590,10 +22590,10 @@
         <v>11000</v>
       </c>
       <c r="D566" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E566" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="567">
@@ -22609,10 +22609,10 @@
         <v>11000</v>
       </c>
       <c r="D567" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E567" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="568">
@@ -22628,10 +22628,10 @@
         <v>11000</v>
       </c>
       <c r="D568" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E568" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="569">
@@ -22647,10 +22647,10 @@
         <v>11000</v>
       </c>
       <c r="D569" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E569" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="570">
@@ -22666,10 +22666,10 @@
         <v>11000</v>
       </c>
       <c r="D570" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E570" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="571">
@@ -22685,10 +22685,10 @@
         <v>11000</v>
       </c>
       <c r="D571" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E571" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="572">
@@ -22704,10 +22704,10 @@
         <v>11000</v>
       </c>
       <c r="D572" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E572" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="573">
@@ -22723,10 +22723,10 @@
         <v>11000</v>
       </c>
       <c r="D573" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="E573" t="n">
-        <v>160</v>
+        <v>41</v>
       </c>
     </row>
     <row r="574">
@@ -22742,10 +22742,10 @@
         <v>13500</v>
       </c>
       <c r="D574" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E574" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="575">
@@ -22761,10 +22761,10 @@
         <v>13500</v>
       </c>
       <c r="D575" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E575" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="576">
@@ -22780,10 +22780,10 @@
         <v>13500</v>
       </c>
       <c r="D576" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E576" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="577">
@@ -22799,10 +22799,10 @@
         <v>13500</v>
       </c>
       <c r="D577" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E577" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="578">
@@ -22818,10 +22818,10 @@
         <v>13500</v>
       </c>
       <c r="D578" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E578" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="579">
@@ -22837,10 +22837,10 @@
         <v>13500</v>
       </c>
       <c r="D579" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E579" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="580">
@@ -22856,10 +22856,10 @@
         <v>13500</v>
       </c>
       <c r="D580" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E580" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="581">
@@ -22875,10 +22875,10 @@
         <v>13500</v>
       </c>
       <c r="D581" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E581" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="582">
@@ -22894,10 +22894,10 @@
         <v>13500</v>
       </c>
       <c r="D582" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E582" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="583">
@@ -22913,10 +22913,10 @@
         <v>13500</v>
       </c>
       <c r="D583" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E583" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="584">
@@ -22932,10 +22932,10 @@
         <v>13500</v>
       </c>
       <c r="D584" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E584" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="585">
@@ -22951,10 +22951,10 @@
         <v>13500</v>
       </c>
       <c r="D585" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E585" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="586">
@@ -22970,10 +22970,10 @@
         <v>13500</v>
       </c>
       <c r="D586" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E586" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="587">
@@ -22989,10 +22989,10 @@
         <v>13500</v>
       </c>
       <c r="D587" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E587" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="588">
@@ -23008,10 +23008,10 @@
         <v>13500</v>
       </c>
       <c r="D588" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E588" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="589">
@@ -23027,10 +23027,10 @@
         <v>13500</v>
       </c>
       <c r="D589" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E589" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="590">
@@ -23046,10 +23046,10 @@
         <v>13500</v>
       </c>
       <c r="D590" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E590" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="591">
@@ -23065,10 +23065,10 @@
         <v>13500</v>
       </c>
       <c r="D591" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E591" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="592">
@@ -23084,10 +23084,10 @@
         <v>13500</v>
       </c>
       <c r="D592" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E592" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="593">
@@ -23103,10 +23103,10 @@
         <v>13500</v>
       </c>
       <c r="D593" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E593" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="594">
@@ -23122,10 +23122,10 @@
         <v>13500</v>
       </c>
       <c r="D594" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E594" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="595">
@@ -23141,10 +23141,10 @@
         <v>13500</v>
       </c>
       <c r="D595" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E595" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="596">
@@ -23160,10 +23160,10 @@
         <v>13500</v>
       </c>
       <c r="D596" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E596" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="597">
@@ -23179,10 +23179,10 @@
         <v>13500</v>
       </c>
       <c r="D597" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E597" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="598">
@@ -23198,10 +23198,10 @@
         <v>13500</v>
       </c>
       <c r="D598" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E598" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="599">
@@ -23217,10 +23217,10 @@
         <v>13500</v>
       </c>
       <c r="D599" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E599" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="600">
@@ -23236,10 +23236,10 @@
         <v>13500</v>
       </c>
       <c r="D600" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E600" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="601">
@@ -23255,10 +23255,10 @@
         <v>13500</v>
       </c>
       <c r="D601" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E601" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="602">
@@ -23274,10 +23274,10 @@
         <v>13500</v>
       </c>
       <c r="D602" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E602" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="603">
@@ -23293,10 +23293,10 @@
         <v>13500</v>
       </c>
       <c r="D603" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E603" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="604">
@@ -23312,10 +23312,10 @@
         <v>13500</v>
       </c>
       <c r="D604" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E604" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="605">
@@ -23331,10 +23331,10 @@
         <v>13500</v>
       </c>
       <c r="D605" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E605" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="606">
@@ -23350,10 +23350,10 @@
         <v>13500</v>
       </c>
       <c r="D606" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E606" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="607">
@@ -23369,10 +23369,10 @@
         <v>13500</v>
       </c>
       <c r="D607" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E607" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="608">
@@ -23388,10 +23388,10 @@
         <v>13500</v>
       </c>
       <c r="D608" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E608" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="609">
@@ -23407,10 +23407,10 @@
         <v>13500</v>
       </c>
       <c r="D609" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E609" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="610">
@@ -23426,10 +23426,10 @@
         <v>13500</v>
       </c>
       <c r="D610" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E610" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="611">
@@ -23445,10 +23445,10 @@
         <v>13500</v>
       </c>
       <c r="D611" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E611" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="612">
@@ -23464,10 +23464,10 @@
         <v>13500</v>
       </c>
       <c r="D612" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E612" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="613">
@@ -23483,10 +23483,10 @@
         <v>13500</v>
       </c>
       <c r="D613" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E613" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="614">
@@ -23502,10 +23502,10 @@
         <v>13500</v>
       </c>
       <c r="D614" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E614" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="615">
@@ -23521,10 +23521,10 @@
         <v>13500</v>
       </c>
       <c r="D615" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E615" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="616">
@@ -23540,10 +23540,10 @@
         <v>13500</v>
       </c>
       <c r="D616" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E616" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="617">
@@ -23559,10 +23559,10 @@
         <v>13500</v>
       </c>
       <c r="D617" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E617" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="618">
@@ -23578,10 +23578,10 @@
         <v>13500</v>
       </c>
       <c r="D618" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E618" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="619">
@@ -23597,10 +23597,10 @@
         <v>13500</v>
       </c>
       <c r="D619" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E619" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="620">
@@ -23616,10 +23616,10 @@
         <v>13500</v>
       </c>
       <c r="D620" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E620" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="621">
@@ -23635,10 +23635,10 @@
         <v>13500</v>
       </c>
       <c r="D621" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E621" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="622">
@@ -23654,10 +23654,10 @@
         <v>13500</v>
       </c>
       <c r="D622" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E622" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="623">
@@ -23673,10 +23673,10 @@
         <v>13500</v>
       </c>
       <c r="D623" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E623" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="624">
@@ -23692,10 +23692,10 @@
         <v>13500</v>
       </c>
       <c r="D624" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E624" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="625">
@@ -23711,10 +23711,10 @@
         <v>13500</v>
       </c>
       <c r="D625" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E625" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
     <row r="626">
@@ -23730,10 +23730,10 @@
         <v>7800</v>
       </c>
       <c r="D626" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E626" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="627">
@@ -23749,10 +23749,10 @@
         <v>7800</v>
       </c>
       <c r="D627" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E627" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="628">
@@ -23768,10 +23768,10 @@
         <v>7800</v>
       </c>
       <c r="D628" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E628" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="629">
@@ -23787,10 +23787,10 @@
         <v>7800</v>
       </c>
       <c r="D629" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E629" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="630">
@@ -23806,10 +23806,10 @@
         <v>7800</v>
       </c>
       <c r="D630" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E630" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="631">
@@ -23825,10 +23825,10 @@
         <v>7800</v>
       </c>
       <c r="D631" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E631" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="632">
@@ -23844,10 +23844,10 @@
         <v>7800</v>
       </c>
       <c r="D632" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E632" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="633">
@@ -23863,10 +23863,10 @@
         <v>7800</v>
       </c>
       <c r="D633" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E633" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="634">
@@ -23882,10 +23882,10 @@
         <v>7800</v>
       </c>
       <c r="D634" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E634" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="635">
@@ -23901,10 +23901,10 @@
         <v>7800</v>
       </c>
       <c r="D635" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E635" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="636">
@@ -23920,10 +23920,10 @@
         <v>7800</v>
       </c>
       <c r="D636" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E636" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="637">
@@ -23939,10 +23939,10 @@
         <v>7800</v>
       </c>
       <c r="D637" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E637" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="638">
@@ -23958,10 +23958,10 @@
         <v>7800</v>
       </c>
       <c r="D638" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E638" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="639">
@@ -23977,10 +23977,10 @@
         <v>7800</v>
       </c>
       <c r="D639" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E639" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="640">
@@ -23996,10 +23996,10 @@
         <v>7800</v>
       </c>
       <c r="D640" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E640" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="641">
@@ -24015,10 +24015,10 @@
         <v>7800</v>
       </c>
       <c r="D641" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E641" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="642">
@@ -24034,10 +24034,10 @@
         <v>7800</v>
       </c>
       <c r="D642" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E642" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="643">
@@ -24053,10 +24053,10 @@
         <v>7800</v>
       </c>
       <c r="D643" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E643" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="644">
@@ -24072,10 +24072,10 @@
         <v>7800</v>
       </c>
       <c r="D644" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E644" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="645">
@@ -24091,10 +24091,10 @@
         <v>7800</v>
       </c>
       <c r="D645" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E645" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="646">
@@ -24110,10 +24110,10 @@
         <v>7800</v>
       </c>
       <c r="D646" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E646" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="647">
@@ -24129,10 +24129,10 @@
         <v>7800</v>
       </c>
       <c r="D647" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E647" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="648">
@@ -24148,10 +24148,10 @@
         <v>7800</v>
       </c>
       <c r="D648" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E648" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="649">
@@ -24167,10 +24167,10 @@
         <v>7800</v>
       </c>
       <c r="D649" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E649" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="650">
@@ -24186,10 +24186,10 @@
         <v>7800</v>
       </c>
       <c r="D650" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E650" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="651">
@@ -24205,10 +24205,10 @@
         <v>7800</v>
       </c>
       <c r="D651" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E651" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="652">
@@ -24224,10 +24224,10 @@
         <v>7800</v>
       </c>
       <c r="D652" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E652" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="653">
@@ -24243,10 +24243,10 @@
         <v>7800</v>
       </c>
       <c r="D653" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E653" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="654">
@@ -24262,10 +24262,10 @@
         <v>7800</v>
       </c>
       <c r="D654" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E654" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="655">
@@ -24281,10 +24281,10 @@
         <v>7800</v>
       </c>
       <c r="D655" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E655" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="656">
@@ -24300,10 +24300,10 @@
         <v>7800</v>
       </c>
       <c r="D656" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E656" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="657">
@@ -24319,10 +24319,10 @@
         <v>7800</v>
       </c>
       <c r="D657" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E657" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="658">
@@ -24338,10 +24338,10 @@
         <v>7800</v>
       </c>
       <c r="D658" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E658" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="659">
@@ -24357,10 +24357,10 @@
         <v>7800</v>
       </c>
       <c r="D659" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E659" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="660">
@@ -24376,10 +24376,10 @@
         <v>7800</v>
       </c>
       <c r="D660" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E660" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="661">
@@ -24395,10 +24395,10 @@
         <v>7800</v>
       </c>
       <c r="D661" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E661" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="662">
@@ -24414,10 +24414,10 @@
         <v>7800</v>
       </c>
       <c r="D662" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E662" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="663">
@@ -24433,10 +24433,10 @@
         <v>7800</v>
       </c>
       <c r="D663" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E663" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="664">
@@ -24452,10 +24452,10 @@
         <v>7800</v>
       </c>
       <c r="D664" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E664" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="665">
@@ -24471,10 +24471,10 @@
         <v>7800</v>
       </c>
       <c r="D665" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E665" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="666">
@@ -24490,10 +24490,10 @@
         <v>7800</v>
       </c>
       <c r="D666" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E666" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="667">
@@ -24509,10 +24509,10 @@
         <v>7800</v>
       </c>
       <c r="D667" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E667" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="668">
@@ -24528,10 +24528,10 @@
         <v>7800</v>
       </c>
       <c r="D668" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E668" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="669">
@@ -24547,10 +24547,10 @@
         <v>7800</v>
       </c>
       <c r="D669" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E669" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="670">
@@ -24566,10 +24566,10 @@
         <v>7800</v>
       </c>
       <c r="D670" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E670" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="671">
@@ -24585,10 +24585,10 @@
         <v>7800</v>
       </c>
       <c r="D671" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E671" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="672">
@@ -24604,10 +24604,10 @@
         <v>7800</v>
       </c>
       <c r="D672" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E672" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="673">
@@ -24623,10 +24623,10 @@
         <v>7800</v>
       </c>
       <c r="D673" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E673" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="674">
@@ -24642,10 +24642,10 @@
         <v>7800</v>
       </c>
       <c r="D674" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E674" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="675">
@@ -24661,10 +24661,10 @@
         <v>7800</v>
       </c>
       <c r="D675" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E675" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="676">
@@ -24680,10 +24680,10 @@
         <v>7800</v>
       </c>
       <c r="D676" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E676" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
     <row r="677">
@@ -24699,10 +24699,10 @@
         <v>7800</v>
       </c>
       <c r="D677" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E677" t="n">
-        <v>250</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -25603,7 +25603,7 @@
         <v>46.5</v>
       </c>
       <c r="F2" t="n">
-        <v>3000</v>
+        <v>768</v>
       </c>
     </row>
     <row r="3">
@@ -25629,7 +25629,7 @@
         <v>46.5</v>
       </c>
       <c r="F3" t="n">
-        <v>3000</v>
+        <v>768</v>
       </c>
     </row>
     <row r="4">
@@ -25655,7 +25655,7 @@
         <v>81</v>
       </c>
       <c r="F4" t="n">
-        <v>3000</v>
+        <v>768</v>
       </c>
     </row>
     <row r="5">
@@ -25681,7 +25681,7 @@
         <v>81</v>
       </c>
       <c r="F5" t="n">
-        <v>3000</v>
+        <v>768</v>
       </c>
     </row>
     <row r="6">
@@ -25707,7 +25707,7 @@
         <v>123</v>
       </c>
       <c r="F6" t="n">
-        <v>3000</v>
+        <v>768</v>
       </c>
     </row>
     <row r="7">
@@ -25733,7 +25733,7 @@
         <v>123</v>
       </c>
       <c r="F7" t="n">
-        <v>3000</v>
+        <v>768</v>
       </c>
     </row>
     <row r="8">
@@ -25759,7 +25759,7 @@
         <v>46.5</v>
       </c>
       <c r="F8" t="n">
-        <v>500</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9">
@@ -25785,7 +25785,7 @@
         <v>46.5</v>
       </c>
       <c r="F9" t="n">
-        <v>500</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10">
@@ -25811,7 +25811,7 @@
         <v>81</v>
       </c>
       <c r="F10" t="n">
-        <v>500</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
@@ -25837,7 +25837,7 @@
         <v>81</v>
       </c>
       <c r="F11" t="n">
-        <v>500</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12">
@@ -25863,7 +25863,7 @@
         <v>123</v>
       </c>
       <c r="F12" t="n">
-        <v>500</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -25889,7 +25889,7 @@
         <v>123</v>
       </c>
       <c r="F13" t="n">
-        <v>500</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -25915,7 +25915,7 @@
         <v>46.5</v>
       </c>
       <c r="F14" t="n">
-        <v>1000</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15">
@@ -25941,7 +25941,7 @@
         <v>46.5</v>
       </c>
       <c r="F15" t="n">
-        <v>1000</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16">
@@ -25967,7 +25967,7 @@
         <v>81</v>
       </c>
       <c r="F16" t="n">
-        <v>1000</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17">
@@ -25993,7 +25993,7 @@
         <v>81</v>
       </c>
       <c r="F17" t="n">
-        <v>1000</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18">
@@ -26019,7 +26019,7 @@
         <v>123</v>
       </c>
       <c r="F18" t="n">
-        <v>1000</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19">
@@ -26045,7 +26045,7 @@
         <v>123</v>
       </c>
       <c r="F19" t="n">
-        <v>1000</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -26983,10 +26983,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>900</v>
+        <v>230</v>
       </c>
       <c r="E2" t="n">
-        <v>5000</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="3">
@@ -27006,10 +27006,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>550</v>
+        <v>140</v>
       </c>
       <c r="E3" t="n">
-        <v>4000</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="4">
@@ -27029,10 +27029,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="E4" t="n">
-        <v>3000</v>
+        <v>768</v>
       </c>
     </row>
     <row r="5">
@@ -27052,10 +27052,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>230</v>
+        <v>40</v>
       </c>
       <c r="E5" t="n">
-        <v>1500</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6">
@@ -27075,10 +27075,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>320</v>
+        <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>2500</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -27145,7 +27145,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11665</v>
+        <v>2981</v>
       </c>
       <c r="D2" t="n">
         <v>4.463</v>
@@ -27167,7 +27167,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11545</v>
+        <v>2950</v>
       </c>
       <c r="D3" t="n">
         <v>4.424</v>
@@ -27189,7 +27189,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11978</v>
+        <v>3061</v>
       </c>
       <c r="D4" t="n">
         <v>4.384</v>
@@ -27211,7 +27211,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12012</v>
+        <v>3070</v>
       </c>
       <c r="D5" t="n">
         <v>4.342</v>
@@ -27233,7 +27233,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13020</v>
+        <v>3327</v>
       </c>
       <c r="D6" t="n">
         <v>4.3</v>
@@ -27255,7 +27255,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14687</v>
+        <v>3753</v>
       </c>
       <c r="D7" t="n">
         <v>4.258</v>
@@ -27277,7 +27277,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16579</v>
+        <v>4237</v>
       </c>
       <c r="D8" t="n">
         <v>4.216</v>
@@ -27299,7 +27299,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16469</v>
+        <v>4209</v>
       </c>
       <c r="D9" t="n">
         <v>4.176</v>
@@ -27321,7 +27321,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16543</v>
+        <v>4228</v>
       </c>
       <c r="D10" t="n">
         <v>4.137</v>
@@ -27343,7 +27343,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>18227</v>
+        <v>4658</v>
       </c>
       <c r="D11" t="n">
         <v>4.101</v>
@@ -27365,7 +27365,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>20648</v>
+        <v>5277</v>
       </c>
       <c r="D12" t="n">
         <v>4.068</v>
@@ -27387,7 +27387,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>22555</v>
+        <v>5764</v>
       </c>
       <c r="D13" t="n">
         <v>4.038</v>
@@ -27409,7 +27409,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>22317</v>
+        <v>5703</v>
       </c>
       <c r="D14" t="n">
         <v>4.012</v>
@@ -27431,7 +27431,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>23676</v>
+        <v>6051</v>
       </c>
       <c r="D15" t="n">
         <v>3.99</v>
@@ -27453,7 +27453,7 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>24440</v>
+        <v>6246</v>
       </c>
       <c r="D16" t="n">
         <v>3.973</v>
@@ -27475,7 +27475,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>24931</v>
+        <v>6371</v>
       </c>
       <c r="D17" t="n">
         <v>3.96</v>
@@ -27497,7 +27497,7 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>25396</v>
+        <v>6490</v>
       </c>
       <c r="D18" t="n">
         <v>3.953</v>
@@ -27519,7 +27519,7 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>24493</v>
+        <v>6259</v>
       </c>
       <c r="D19" t="n">
         <v>3.95</v>
@@ -27541,7 +27541,7 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>24766</v>
+        <v>6329</v>
       </c>
       <c r="D20" t="n">
         <v>3.953</v>
@@ -27563,7 +27563,7 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>24019</v>
+        <v>6138</v>
       </c>
       <c r="D21" t="n">
         <v>3.96</v>
@@ -27585,7 +27585,7 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>23971</v>
+        <v>6126</v>
       </c>
       <c r="D22" t="n">
         <v>3.973</v>
@@ -27607,7 +27607,7 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>23792</v>
+        <v>6080</v>
       </c>
       <c r="D23" t="n">
         <v>3.99</v>
@@ -27629,7 +27629,7 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>23414</v>
+        <v>5984</v>
       </c>
       <c r="D24" t="n">
         <v>4.012</v>
@@ -27651,7 +27651,7 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>21896</v>
+        <v>5596</v>
       </c>
       <c r="D25" t="n">
         <v>4.038</v>
@@ -27673,7 +27673,7 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>20768</v>
+        <v>5307</v>
       </c>
       <c r="D26" t="n">
         <v>4.068</v>
@@ -27695,7 +27695,7 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>20791</v>
+        <v>5313</v>
       </c>
       <c r="D27" t="n">
         <v>4.101</v>
@@ -27717,7 +27717,7 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>20132</v>
+        <v>5145</v>
       </c>
       <c r="D28" t="n">
         <v>4.137</v>
@@ -27739,7 +27739,7 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>19148</v>
+        <v>4893</v>
       </c>
       <c r="D29" t="n">
         <v>4.176</v>
@@ -27761,7 +27761,7 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>18227</v>
+        <v>4658</v>
       </c>
       <c r="D30" t="n">
         <v>4.216</v>
@@ -27783,7 +27783,7 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>18232</v>
+        <v>4659</v>
       </c>
       <c r="D31" t="n">
         <v>4.258</v>
@@ -27805,7 +27805,7 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>17978</v>
+        <v>4594</v>
       </c>
       <c r="D32" t="n">
         <v>4.3</v>
@@ -27827,7 +27827,7 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>16620</v>
+        <v>4247</v>
       </c>
       <c r="D33" t="n">
         <v>4.342</v>
@@ -27849,7 +27849,7 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>15902</v>
+        <v>4064</v>
       </c>
       <c r="D34" t="n">
         <v>4.384</v>
@@ -27871,7 +27871,7 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>15829</v>
+        <v>4045</v>
       </c>
       <c r="D35" t="n">
         <v>4.424</v>
@@ -27893,7 +27893,7 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>15821</v>
+        <v>4043</v>
       </c>
       <c r="D36" t="n">
         <v>4.463</v>
@@ -27915,7 +27915,7 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>15588</v>
+        <v>3984</v>
       </c>
       <c r="D37" t="n">
         <v>4.499</v>
@@ -27937,7 +27937,7 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>14954</v>
+        <v>3822</v>
       </c>
       <c r="D38" t="n">
         <v>4.532</v>
@@ -27959,7 +27959,7 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>14791</v>
+        <v>3780</v>
       </c>
       <c r="D39" t="n">
         <v>4.562</v>
@@ -27981,7 +27981,7 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>14794</v>
+        <v>3781</v>
       </c>
       <c r="D40" t="n">
         <v>4.588</v>
@@ -28003,7 +28003,7 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>14774</v>
+        <v>3776</v>
       </c>
       <c r="D41" t="n">
         <v>4.61</v>
@@ -28025,7 +28025,7 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>14442</v>
+        <v>3691</v>
       </c>
       <c r="D42" t="n">
         <v>4.627</v>
@@ -28047,7 +28047,7 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>14048</v>
+        <v>3590</v>
       </c>
       <c r="D43" t="n">
         <v>4.64</v>
@@ -28069,7 +28069,7 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>13795</v>
+        <v>3526</v>
       </c>
       <c r="D44" t="n">
         <v>4.647</v>
@@ -28091,7 +28091,7 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>13517</v>
+        <v>3454</v>
       </c>
       <c r="D45" t="n">
         <v>4.65</v>
@@ -28113,7 +28113,7 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>13028</v>
+        <v>3329</v>
       </c>
       <c r="D46" t="n">
         <v>4.647</v>
@@ -28135,7 +28135,7 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>12582</v>
+        <v>3215</v>
       </c>
       <c r="D47" t="n">
         <v>4.64</v>
@@ -28157,7 +28157,7 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>12705</v>
+        <v>3247</v>
       </c>
       <c r="D48" t="n">
         <v>4.627</v>
@@ -28179,7 +28179,7 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>12583</v>
+        <v>3216</v>
       </c>
       <c r="D49" t="n">
         <v>4.61</v>
@@ -28201,7 +28201,7 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>12317</v>
+        <v>3148</v>
       </c>
       <c r="D50" t="n">
         <v>4.588</v>
@@ -28223,7 +28223,7 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>11856</v>
+        <v>3030</v>
       </c>
       <c r="D51" t="n">
         <v>4.562</v>
@@ -28245,7 +28245,7 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>11546</v>
+        <v>2951</v>
       </c>
       <c r="D52" t="n">
         <v>4.532</v>
@@ -28267,7 +28267,7 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>11605</v>
+        <v>2966</v>
       </c>
       <c r="D53" t="n">
         <v>4.499</v>
@@ -28289,7 +28289,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>7111</v>
+        <v>1810</v>
       </c>
       <c r="D54" t="n">
         <v>4.513</v>
@@ -28311,7 +28311,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>7303</v>
+        <v>1859</v>
       </c>
       <c r="D55" t="n">
         <v>4.474</v>
@@ -28333,7 +28333,7 @@
         <v>3</v>
       </c>
       <c r="C56" t="n">
-        <v>7353</v>
+        <v>1872</v>
       </c>
       <c r="D56" t="n">
         <v>4.434</v>
@@ -28355,7 +28355,7 @@
         <v>4</v>
       </c>
       <c r="C57" t="n">
-        <v>7334</v>
+        <v>1867</v>
       </c>
       <c r="D57" t="n">
         <v>4.392</v>
@@ -28377,7 +28377,7 @@
         <v>5</v>
       </c>
       <c r="C58" t="n">
-        <v>8281</v>
+        <v>2108</v>
       </c>
       <c r="D58" t="n">
         <v>4.35</v>
@@ -28399,7 +28399,7 @@
         <v>6</v>
       </c>
       <c r="C59" t="n">
-        <v>9432</v>
+        <v>2401</v>
       </c>
       <c r="D59" t="n">
         <v>4.308</v>
@@ -28421,7 +28421,7 @@
         <v>7</v>
       </c>
       <c r="C60" t="n">
-        <v>10004</v>
+        <v>2546</v>
       </c>
       <c r="D60" t="n">
         <v>4.266</v>
@@ -28443,7 +28443,7 @@
         <v>8</v>
       </c>
       <c r="C61" t="n">
-        <v>10283</v>
+        <v>2617</v>
       </c>
       <c r="D61" t="n">
         <v>4.226</v>
@@ -28465,7 +28465,7 @@
         <v>9</v>
       </c>
       <c r="C62" t="n">
-        <v>9880</v>
+        <v>2515</v>
       </c>
       <c r="D62" t="n">
         <v>4.187</v>
@@ -28487,7 +28487,7 @@
         <v>10</v>
       </c>
       <c r="C63" t="n">
-        <v>11191</v>
+        <v>2849</v>
       </c>
       <c r="D63" t="n">
         <v>4.151</v>
@@ -28509,7 +28509,7 @@
         <v>11</v>
       </c>
       <c r="C64" t="n">
-        <v>12390</v>
+        <v>3154</v>
       </c>
       <c r="D64" t="n">
         <v>4.118</v>
@@ -28531,7 +28531,7 @@
         <v>12</v>
       </c>
       <c r="C65" t="n">
-        <v>13591</v>
+        <v>3460</v>
       </c>
       <c r="D65" t="n">
         <v>4.088</v>
@@ -28553,7 +28553,7 @@
         <v>13</v>
       </c>
       <c r="C66" t="n">
-        <v>13616</v>
+        <v>3466</v>
       </c>
       <c r="D66" t="n">
         <v>4.062</v>
@@ -28575,7 +28575,7 @@
         <v>14</v>
       </c>
       <c r="C67" t="n">
-        <v>14213</v>
+        <v>3618</v>
       </c>
       <c r="D67" t="n">
         <v>4.04</v>
@@ -28597,7 +28597,7 @@
         <v>15</v>
       </c>
       <c r="C68" t="n">
-        <v>14542</v>
+        <v>3702</v>
       </c>
       <c r="D68" t="n">
         <v>4.023</v>
@@ -28619,7 +28619,7 @@
         <v>16</v>
       </c>
       <c r="C69" t="n">
-        <v>15086</v>
+        <v>3840</v>
       </c>
       <c r="D69" t="n">
         <v>4.01</v>
@@ -28641,7 +28641,7 @@
         <v>17</v>
       </c>
       <c r="C70" t="n">
-        <v>15387</v>
+        <v>3917</v>
       </c>
       <c r="D70" t="n">
         <v>4.003</v>
@@ -28663,7 +28663,7 @@
         <v>18</v>
       </c>
       <c r="C71" t="n">
-        <v>14913</v>
+        <v>3796</v>
       </c>
       <c r="D71" t="n">
         <v>4</v>
@@ -28685,7 +28685,7 @@
         <v>19</v>
       </c>
       <c r="C72" t="n">
-        <v>14438</v>
+        <v>3675</v>
       </c>
       <c r="D72" t="n">
         <v>4.003</v>
@@ -28707,7 +28707,7 @@
         <v>20</v>
       </c>
       <c r="C73" t="n">
-        <v>14238</v>
+        <v>3624</v>
       </c>
       <c r="D73" t="n">
         <v>4.01</v>
@@ -28729,7 +28729,7 @@
         <v>21</v>
       </c>
       <c r="C74" t="n">
-        <v>14284</v>
+        <v>3636</v>
       </c>
       <c r="D74" t="n">
         <v>4.023</v>
@@ -28751,7 +28751,7 @@
         <v>22</v>
       </c>
       <c r="C75" t="n">
-        <v>14592</v>
+        <v>3714</v>
       </c>
       <c r="D75" t="n">
         <v>4.04</v>
@@ -28773,7 +28773,7 @@
         <v>23</v>
       </c>
       <c r="C76" t="n">
-        <v>13907</v>
+        <v>3540</v>
       </c>
       <c r="D76" t="n">
         <v>4.062</v>
@@ -28795,7 +28795,7 @@
         <v>24</v>
       </c>
       <c r="C77" t="n">
-        <v>13408</v>
+        <v>3413</v>
       </c>
       <c r="D77" t="n">
         <v>4.088</v>
@@ -28817,7 +28817,7 @@
         <v>25</v>
       </c>
       <c r="C78" t="n">
-        <v>12582</v>
+        <v>3203</v>
       </c>
       <c r="D78" t="n">
         <v>4.118</v>
@@ -28839,7 +28839,7 @@
         <v>26</v>
       </c>
       <c r="C79" t="n">
-        <v>12694</v>
+        <v>3231</v>
       </c>
       <c r="D79" t="n">
         <v>4.151</v>
@@ -28861,7 +28861,7 @@
         <v>27</v>
       </c>
       <c r="C80" t="n">
-        <v>12238</v>
+        <v>3115</v>
       </c>
       <c r="D80" t="n">
         <v>4.187</v>
@@ -28883,7 +28883,7 @@
         <v>28</v>
       </c>
       <c r="C81" t="n">
-        <v>11531</v>
+        <v>2935</v>
       </c>
       <c r="D81" t="n">
         <v>4.226</v>
@@ -28905,7 +28905,7 @@
         <v>29</v>
       </c>
       <c r="C82" t="n">
-        <v>11121</v>
+        <v>2831</v>
       </c>
       <c r="D82" t="n">
         <v>4.266</v>
@@ -28927,7 +28927,7 @@
         <v>30</v>
       </c>
       <c r="C83" t="n">
-        <v>10936</v>
+        <v>2784</v>
       </c>
       <c r="D83" t="n">
         <v>4.308</v>
@@ -28949,7 +28949,7 @@
         <v>31</v>
       </c>
       <c r="C84" t="n">
-        <v>10583</v>
+        <v>2694</v>
       </c>
       <c r="D84" t="n">
         <v>4.35</v>
@@ -28971,7 +28971,7 @@
         <v>32</v>
       </c>
       <c r="C85" t="n">
-        <v>10178</v>
+        <v>2591</v>
       </c>
       <c r="D85" t="n">
         <v>4.392</v>
@@ -28993,7 +28993,7 @@
         <v>33</v>
       </c>
       <c r="C86" t="n">
-        <v>9656</v>
+        <v>2458</v>
       </c>
       <c r="D86" t="n">
         <v>4.434</v>
@@ -29015,7 +29015,7 @@
         <v>34</v>
       </c>
       <c r="C87" t="n">
-        <v>9904</v>
+        <v>2521</v>
       </c>
       <c r="D87" t="n">
         <v>4.474</v>
@@ -29037,7 +29037,7 @@
         <v>35</v>
       </c>
       <c r="C88" t="n">
-        <v>9562</v>
+        <v>2434</v>
       </c>
       <c r="D88" t="n">
         <v>4.513</v>
@@ -29059,7 +29059,7 @@
         <v>36</v>
       </c>
       <c r="C89" t="n">
-        <v>9429</v>
+        <v>2400</v>
       </c>
       <c r="D89" t="n">
         <v>4.549</v>
@@ -29081,7 +29081,7 @@
         <v>37</v>
       </c>
       <c r="C90" t="n">
-        <v>9292</v>
+        <v>2365</v>
       </c>
       <c r="D90" t="n">
         <v>4.582</v>
@@ -29103,7 +29103,7 @@
         <v>38</v>
       </c>
       <c r="C91" t="n">
-        <v>9287</v>
+        <v>2364</v>
       </c>
       <c r="D91" t="n">
         <v>4.612</v>
@@ -29125,7 +29125,7 @@
         <v>39</v>
       </c>
       <c r="C92" t="n">
-        <v>9317</v>
+        <v>2372</v>
       </c>
       <c r="D92" t="n">
         <v>4.638</v>
@@ -29147,7 +29147,7 @@
         <v>40</v>
       </c>
       <c r="C93" t="n">
-        <v>9010</v>
+        <v>2293</v>
       </c>
       <c r="D93" t="n">
         <v>4.66</v>
@@ -29169,7 +29169,7 @@
         <v>41</v>
       </c>
       <c r="C94" t="n">
-        <v>8765</v>
+        <v>2231</v>
       </c>
       <c r="D94" t="n">
         <v>4.677</v>
@@ -29191,7 +29191,7 @@
         <v>42</v>
       </c>
       <c r="C95" t="n">
-        <v>8608</v>
+        <v>2191</v>
       </c>
       <c r="D95" t="n">
         <v>4.69</v>
@@ -29213,7 +29213,7 @@
         <v>43</v>
       </c>
       <c r="C96" t="n">
-        <v>8401</v>
+        <v>2138</v>
       </c>
       <c r="D96" t="n">
         <v>4.697</v>
@@ -29235,7 +29235,7 @@
         <v>44</v>
       </c>
       <c r="C97" t="n">
-        <v>8168</v>
+        <v>2079</v>
       </c>
       <c r="D97" t="n">
         <v>4.7</v>
@@ -29257,7 +29257,7 @@
         <v>45</v>
       </c>
       <c r="C98" t="n">
-        <v>7919</v>
+        <v>2016</v>
       </c>
       <c r="D98" t="n">
         <v>4.697</v>
@@ -29279,7 +29279,7 @@
         <v>46</v>
       </c>
       <c r="C99" t="n">
-        <v>7693</v>
+        <v>1958</v>
       </c>
       <c r="D99" t="n">
         <v>4.69</v>
@@ -29301,7 +29301,7 @@
         <v>47</v>
       </c>
       <c r="C100" t="n">
-        <v>7856</v>
+        <v>2000</v>
       </c>
       <c r="D100" t="n">
         <v>4.677</v>
@@ -29323,7 +29323,7 @@
         <v>48</v>
       </c>
       <c r="C101" t="n">
-        <v>7704</v>
+        <v>1961</v>
       </c>
       <c r="D101" t="n">
         <v>4.66</v>
@@ -29345,7 +29345,7 @@
         <v>49</v>
       </c>
       <c r="C102" t="n">
-        <v>7564</v>
+        <v>1925</v>
       </c>
       <c r="D102" t="n">
         <v>4.638</v>
@@ -29367,7 +29367,7 @@
         <v>50</v>
       </c>
       <c r="C103" t="n">
-        <v>7549</v>
+        <v>1922</v>
       </c>
       <c r="D103" t="n">
         <v>4.612</v>
@@ -29389,7 +29389,7 @@
         <v>51</v>
       </c>
       <c r="C104" t="n">
-        <v>7164</v>
+        <v>1824</v>
       </c>
       <c r="D104" t="n">
         <v>4.582</v>
@@ -29411,7 +29411,7 @@
         <v>52</v>
       </c>
       <c r="C105" t="n">
-        <v>7283</v>
+        <v>1854</v>
       </c>
       <c r="D105" t="n">
         <v>4.549</v>
@@ -29433,7 +29433,7 @@
         <v>1</v>
       </c>
       <c r="C106" t="n">
-        <v>6985</v>
+        <v>1816</v>
       </c>
       <c r="D106" t="n">
         <v>4.213</v>
@@ -29455,7 +29455,7 @@
         <v>2</v>
       </c>
       <c r="C107" t="n">
-        <v>7114</v>
+        <v>1850</v>
       </c>
       <c r="D107" t="n">
         <v>4.174</v>
@@ -29477,7 +29477,7 @@
         <v>3</v>
       </c>
       <c r="C108" t="n">
-        <v>7085</v>
+        <v>1842</v>
       </c>
       <c r="D108" t="n">
         <v>4.134</v>
@@ -29499,7 +29499,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="n">
-        <v>7151</v>
+        <v>1859</v>
       </c>
       <c r="D109" t="n">
         <v>4.092</v>
@@ -29521,7 +29521,7 @@
         <v>5</v>
       </c>
       <c r="C110" t="n">
-        <v>7983</v>
+        <v>2076</v>
       </c>
       <c r="D110" t="n">
         <v>4.05</v>
@@ -29543,7 +29543,7 @@
         <v>6</v>
       </c>
       <c r="C111" t="n">
-        <v>8358</v>
+        <v>2173</v>
       </c>
       <c r="D111" t="n">
         <v>4.008</v>
@@ -29565,7 +29565,7 @@
         <v>7</v>
       </c>
       <c r="C112" t="n">
-        <v>9338</v>
+        <v>2428</v>
       </c>
       <c r="D112" t="n">
         <v>3.966</v>
@@ -29587,7 +29587,7 @@
         <v>8</v>
       </c>
       <c r="C113" t="n">
-        <v>9311</v>
+        <v>2421</v>
       </c>
       <c r="D113" t="n">
         <v>3.926</v>
@@ -29609,7 +29609,7 @@
         <v>9</v>
       </c>
       <c r="C114" t="n">
-        <v>9195</v>
+        <v>2391</v>
       </c>
       <c r="D114" t="n">
         <v>3.887</v>
@@ -29631,7 +29631,7 @@
         <v>10</v>
       </c>
       <c r="C115" t="n">
-        <v>9909</v>
+        <v>2576</v>
       </c>
       <c r="D115" t="n">
         <v>3.851</v>
@@ -29653,7 +29653,7 @@
         <v>11</v>
       </c>
       <c r="C116" t="n">
-        <v>10992</v>
+        <v>2858</v>
       </c>
       <c r="D116" t="n">
         <v>3.818</v>
@@ -29675,7 +29675,7 @@
         <v>12</v>
       </c>
       <c r="C117" t="n">
-        <v>11738</v>
+        <v>3052</v>
       </c>
       <c r="D117" t="n">
         <v>3.788</v>
@@ -29697,7 +29697,7 @@
         <v>13</v>
       </c>
       <c r="C118" t="n">
-        <v>11873</v>
+        <v>3087</v>
       </c>
       <c r="D118" t="n">
         <v>3.762</v>
@@ -29719,7 +29719,7 @@
         <v>14</v>
       </c>
       <c r="C119" t="n">
-        <v>12275</v>
+        <v>3191</v>
       </c>
       <c r="D119" t="n">
         <v>3.74</v>
@@ -29741,7 +29741,7 @@
         <v>15</v>
       </c>
       <c r="C120" t="n">
-        <v>13015</v>
+        <v>3384</v>
       </c>
       <c r="D120" t="n">
         <v>3.723</v>
@@ -29763,7 +29763,7 @@
         <v>16</v>
       </c>
       <c r="C121" t="n">
-        <v>13101</v>
+        <v>3406</v>
       </c>
       <c r="D121" t="n">
         <v>3.71</v>
@@ -29785,7 +29785,7 @@
         <v>17</v>
       </c>
       <c r="C122" t="n">
-        <v>12946</v>
+        <v>3366</v>
       </c>
       <c r="D122" t="n">
         <v>3.703</v>
@@ -29807,7 +29807,7 @@
         <v>18</v>
       </c>
       <c r="C123" t="n">
-        <v>13002</v>
+        <v>3381</v>
       </c>
       <c r="D123" t="n">
         <v>3.7</v>
@@ -29829,7 +29829,7 @@
         <v>19</v>
       </c>
       <c r="C124" t="n">
-        <v>12829</v>
+        <v>3336</v>
       </c>
       <c r="D124" t="n">
         <v>3.703</v>
@@ -29851,7 +29851,7 @@
         <v>20</v>
       </c>
       <c r="C125" t="n">
-        <v>12863</v>
+        <v>3344</v>
       </c>
       <c r="D125" t="n">
         <v>3.71</v>
@@ -29873,7 +29873,7 @@
         <v>21</v>
       </c>
       <c r="C126" t="n">
-        <v>12764</v>
+        <v>3319</v>
       </c>
       <c r="D126" t="n">
         <v>3.723</v>
@@ -29895,7 +29895,7 @@
         <v>22</v>
       </c>
       <c r="C127" t="n">
-        <v>12674</v>
+        <v>3295</v>
       </c>
       <c r="D127" t="n">
         <v>3.74</v>
@@ -29917,7 +29917,7 @@
         <v>23</v>
       </c>
       <c r="C128" t="n">
-        <v>12408</v>
+        <v>3226</v>
       </c>
       <c r="D128" t="n">
         <v>3.762</v>
@@ -29939,7 +29939,7 @@
         <v>24</v>
       </c>
       <c r="C129" t="n">
-        <v>11469</v>
+        <v>2982</v>
       </c>
       <c r="D129" t="n">
         <v>3.788</v>
@@ -29961,7 +29961,7 @@
         <v>25</v>
       </c>
       <c r="C130" t="n">
-        <v>11105</v>
+        <v>2887</v>
       </c>
       <c r="D130" t="n">
         <v>3.818</v>
@@ -29983,7 +29983,7 @@
         <v>26</v>
       </c>
       <c r="C131" t="n">
-        <v>11057</v>
+        <v>2875</v>
       </c>
       <c r="D131" t="n">
         <v>3.851</v>
@@ -30005,7 +30005,7 @@
         <v>27</v>
       </c>
       <c r="C132" t="n">
-        <v>10737</v>
+        <v>2792</v>
       </c>
       <c r="D132" t="n">
         <v>3.887</v>
@@ -30027,7 +30027,7 @@
         <v>28</v>
       </c>
       <c r="C133" t="n">
-        <v>10173</v>
+        <v>2645</v>
       </c>
       <c r="D133" t="n">
         <v>3.926</v>
@@ -30049,7 +30049,7 @@
         <v>29</v>
       </c>
       <c r="C134" t="n">
-        <v>10069</v>
+        <v>2618</v>
       </c>
       <c r="D134" t="n">
         <v>3.966</v>
@@ -30071,7 +30071,7 @@
         <v>30</v>
       </c>
       <c r="C135" t="n">
-        <v>9941</v>
+        <v>2585</v>
       </c>
       <c r="D135" t="n">
         <v>4.008</v>
@@ -30093,7 +30093,7 @@
         <v>31</v>
       </c>
       <c r="C136" t="n">
-        <v>9451</v>
+        <v>2457</v>
       </c>
       <c r="D136" t="n">
         <v>4.05</v>
@@ -30115,7 +30115,7 @@
         <v>32</v>
       </c>
       <c r="C137" t="n">
-        <v>9212</v>
+        <v>2395</v>
       </c>
       <c r="D137" t="n">
         <v>4.092</v>
@@ -30137,7 +30137,7 @@
         <v>33</v>
       </c>
       <c r="C138" t="n">
-        <v>9088</v>
+        <v>2363</v>
       </c>
       <c r="D138" t="n">
         <v>4.134</v>
@@ -30159,7 +30159,7 @@
         <v>34</v>
       </c>
       <c r="C139" t="n">
-        <v>9159</v>
+        <v>2381</v>
       </c>
       <c r="D139" t="n">
         <v>4.174</v>
@@ -30181,7 +30181,7 @@
         <v>35</v>
       </c>
       <c r="C140" t="n">
-        <v>9157</v>
+        <v>2381</v>
       </c>
       <c r="D140" t="n">
         <v>4.213</v>
@@ -30203,7 +30203,7 @@
         <v>36</v>
       </c>
       <c r="C141" t="n">
-        <v>9117</v>
+        <v>2371</v>
       </c>
       <c r="D141" t="n">
         <v>4.249</v>
@@ -30225,7 +30225,7 @@
         <v>37</v>
       </c>
       <c r="C142" t="n">
-        <v>8634</v>
+        <v>2245</v>
       </c>
       <c r="D142" t="n">
         <v>4.282</v>
@@ -30247,7 +30247,7 @@
         <v>38</v>
       </c>
       <c r="C143" t="n">
-        <v>8453</v>
+        <v>2198</v>
       </c>
       <c r="D143" t="n">
         <v>4.312</v>
@@ -30269,7 +30269,7 @@
         <v>39</v>
       </c>
       <c r="C144" t="n">
-        <v>8306</v>
+        <v>2160</v>
       </c>
       <c r="D144" t="n">
         <v>4.338</v>
@@ -30291,7 +30291,7 @@
         <v>40</v>
       </c>
       <c r="C145" t="n">
-        <v>8460</v>
+        <v>2200</v>
       </c>
       <c r="D145" t="n">
         <v>4.36</v>
@@ -30313,7 +30313,7 @@
         <v>41</v>
       </c>
       <c r="C146" t="n">
-        <v>8170</v>
+        <v>2124</v>
       </c>
       <c r="D146" t="n">
         <v>4.377</v>
@@ -30335,7 +30335,7 @@
         <v>42</v>
       </c>
       <c r="C147" t="n">
-        <v>8066</v>
+        <v>2097</v>
       </c>
       <c r="D147" t="n">
         <v>4.39</v>
@@ -30357,7 +30357,7 @@
         <v>43</v>
       </c>
       <c r="C148" t="n">
-        <v>8042</v>
+        <v>2091</v>
       </c>
       <c r="D148" t="n">
         <v>4.397</v>
@@ -30379,7 +30379,7 @@
         <v>44</v>
       </c>
       <c r="C149" t="n">
-        <v>7893</v>
+        <v>2052</v>
       </c>
       <c r="D149" t="n">
         <v>4.4</v>
@@ -30401,7 +30401,7 @@
         <v>45</v>
       </c>
       <c r="C150" t="n">
-        <v>7827</v>
+        <v>2035</v>
       </c>
       <c r="D150" t="n">
         <v>4.397</v>
@@ -30423,7 +30423,7 @@
         <v>46</v>
       </c>
       <c r="C151" t="n">
-        <v>7515</v>
+        <v>1954</v>
       </c>
       <c r="D151" t="n">
         <v>4.39</v>
@@ -30445,7 +30445,7 @@
         <v>47</v>
       </c>
       <c r="C152" t="n">
-        <v>7479</v>
+        <v>1945</v>
       </c>
       <c r="D152" t="n">
         <v>4.377</v>
@@ -30467,7 +30467,7 @@
         <v>48</v>
       </c>
       <c r="C153" t="n">
-        <v>7380</v>
+        <v>1919</v>
       </c>
       <c r="D153" t="n">
         <v>4.36</v>
@@ -30489,7 +30489,7 @@
         <v>49</v>
       </c>
       <c r="C154" t="n">
-        <v>7158</v>
+        <v>1861</v>
       </c>
       <c r="D154" t="n">
         <v>4.338</v>
@@ -30511,7 +30511,7 @@
         <v>50</v>
       </c>
       <c r="C155" t="n">
-        <v>7135</v>
+        <v>1855</v>
       </c>
       <c r="D155" t="n">
         <v>4.312</v>
@@ -30533,7 +30533,7 @@
         <v>51</v>
       </c>
       <c r="C156" t="n">
-        <v>7027</v>
+        <v>1827</v>
       </c>
       <c r="D156" t="n">
         <v>4.282</v>
@@ -30555,7 +30555,7 @@
         <v>52</v>
       </c>
       <c r="C157" t="n">
-        <v>7219</v>
+        <v>1877</v>
       </c>
       <c r="D157" t="n">
         <v>4.249</v>
@@ -30577,7 +30577,7 @@
         <v>1</v>
       </c>
       <c r="C158" t="n">
-        <v>3630</v>
+        <v>631</v>
       </c>
       <c r="D158" t="n">
         <v>4.413</v>
@@ -30599,7 +30599,7 @@
         <v>2</v>
       </c>
       <c r="C159" t="n">
-        <v>3692</v>
+        <v>642</v>
       </c>
       <c r="D159" t="n">
         <v>4.374</v>
@@ -30621,7 +30621,7 @@
         <v>3</v>
       </c>
       <c r="C160" t="n">
-        <v>3628</v>
+        <v>631</v>
       </c>
       <c r="D160" t="n">
         <v>4.334</v>
@@ -30643,7 +30643,7 @@
         <v>4</v>
       </c>
       <c r="C161" t="n">
-        <v>3590</v>
+        <v>624</v>
       </c>
       <c r="D161" t="n">
         <v>4.292</v>
@@ -30665,7 +30665,7 @@
         <v>5</v>
       </c>
       <c r="C162" t="n">
-        <v>3819</v>
+        <v>664</v>
       </c>
       <c r="D162" t="n">
         <v>4.25</v>
@@ -30687,7 +30687,7 @@
         <v>6</v>
       </c>
       <c r="C163" t="n">
-        <v>4051</v>
+        <v>705</v>
       </c>
       <c r="D163" t="n">
         <v>4.208</v>
@@ -30709,7 +30709,7 @@
         <v>7</v>
       </c>
       <c r="C164" t="n">
-        <v>4454</v>
+        <v>775</v>
       </c>
       <c r="D164" t="n">
         <v>4.166</v>
@@ -30731,7 +30731,7 @@
         <v>8</v>
       </c>
       <c r="C165" t="n">
-        <v>4263</v>
+        <v>741</v>
       </c>
       <c r="D165" t="n">
         <v>4.126</v>
@@ -30753,7 +30753,7 @@
         <v>9</v>
       </c>
       <c r="C166" t="n">
-        <v>4370</v>
+        <v>760</v>
       </c>
       <c r="D166" t="n">
         <v>4.087</v>
@@ -30775,7 +30775,7 @@
         <v>10</v>
       </c>
       <c r="C167" t="n">
-        <v>4523</v>
+        <v>787</v>
       </c>
       <c r="D167" t="n">
         <v>4.051</v>
@@ -30797,7 +30797,7 @@
         <v>11</v>
       </c>
       <c r="C168" t="n">
-        <v>4923</v>
+        <v>856</v>
       </c>
       <c r="D168" t="n">
         <v>4.018</v>
@@ -30819,7 +30819,7 @@
         <v>12</v>
       </c>
       <c r="C169" t="n">
-        <v>5154</v>
+        <v>896</v>
       </c>
       <c r="D169" t="n">
         <v>3.988</v>
@@ -30841,7 +30841,7 @@
         <v>13</v>
       </c>
       <c r="C170" t="n">
-        <v>5112</v>
+        <v>889</v>
       </c>
       <c r="D170" t="n">
         <v>3.962</v>
@@ -30863,7 +30863,7 @@
         <v>14</v>
       </c>
       <c r="C171" t="n">
-        <v>5260</v>
+        <v>915</v>
       </c>
       <c r="D171" t="n">
         <v>3.94</v>
@@ -30885,7 +30885,7 @@
         <v>15</v>
       </c>
       <c r="C172" t="n">
-        <v>5349</v>
+        <v>930</v>
       </c>
       <c r="D172" t="n">
         <v>3.923</v>
@@ -30907,7 +30907,7 @@
         <v>16</v>
       </c>
       <c r="C173" t="n">
-        <v>5577</v>
+        <v>970</v>
       </c>
       <c r="D173" t="n">
         <v>3.91</v>
@@ -30929,7 +30929,7 @@
         <v>17</v>
       </c>
       <c r="C174" t="n">
-        <v>5503</v>
+        <v>957</v>
       </c>
       <c r="D174" t="n">
         <v>3.903</v>
@@ -30951,7 +30951,7 @@
         <v>18</v>
       </c>
       <c r="C175" t="n">
-        <v>5382</v>
+        <v>936</v>
       </c>
       <c r="D175" t="n">
         <v>3.9</v>
@@ -30973,7 +30973,7 @@
         <v>19</v>
       </c>
       <c r="C176" t="n">
-        <v>5322</v>
+        <v>926</v>
       </c>
       <c r="D176" t="n">
         <v>3.903</v>
@@ -30995,7 +30995,7 @@
         <v>20</v>
       </c>
       <c r="C177" t="n">
-        <v>5383</v>
+        <v>936</v>
       </c>
       <c r="D177" t="n">
         <v>3.91</v>
@@ -31017,7 +31017,7 @@
         <v>21</v>
       </c>
       <c r="C178" t="n">
-        <v>5496</v>
+        <v>956</v>
       </c>
       <c r="D178" t="n">
         <v>3.923</v>
@@ -31039,7 +31039,7 @@
         <v>22</v>
       </c>
       <c r="C179" t="n">
-        <v>5382</v>
+        <v>936</v>
       </c>
       <c r="D179" t="n">
         <v>3.94</v>
@@ -31061,7 +31061,7 @@
         <v>23</v>
       </c>
       <c r="C180" t="n">
-        <v>5213</v>
+        <v>907</v>
       </c>
       <c r="D180" t="n">
         <v>3.962</v>
@@ -31083,7 +31083,7 @@
         <v>24</v>
       </c>
       <c r="C181" t="n">
-        <v>5097</v>
+        <v>886</v>
       </c>
       <c r="D181" t="n">
         <v>3.988</v>
@@ -31105,7 +31105,7 @@
         <v>25</v>
       </c>
       <c r="C182" t="n">
-        <v>5025</v>
+        <v>874</v>
       </c>
       <c r="D182" t="n">
         <v>4.018</v>
@@ -31127,7 +31127,7 @@
         <v>26</v>
       </c>
       <c r="C183" t="n">
-        <v>4944</v>
+        <v>860</v>
       </c>
       <c r="D183" t="n">
         <v>4.051</v>
@@ -31149,7 +31149,7 @@
         <v>27</v>
       </c>
       <c r="C184" t="n">
-        <v>4768</v>
+        <v>829</v>
       </c>
       <c r="D184" t="n">
         <v>4.087</v>
@@ -31171,7 +31171,7 @@
         <v>28</v>
       </c>
       <c r="C185" t="n">
-        <v>4745</v>
+        <v>825</v>
       </c>
       <c r="D185" t="n">
         <v>4.126</v>
@@ -31193,7 +31193,7 @@
         <v>29</v>
       </c>
       <c r="C186" t="n">
-        <v>4566</v>
+        <v>794</v>
       </c>
       <c r="D186" t="n">
         <v>4.166</v>
@@ -31215,7 +31215,7 @@
         <v>30</v>
       </c>
       <c r="C187" t="n">
-        <v>4641</v>
+        <v>807</v>
       </c>
       <c r="D187" t="n">
         <v>4.208</v>
@@ -31237,7 +31237,7 @@
         <v>31</v>
       </c>
       <c r="C188" t="n">
-        <v>4451</v>
+        <v>774</v>
       </c>
       <c r="D188" t="n">
         <v>4.25</v>
@@ -31259,7 +31259,7 @@
         <v>32</v>
       </c>
       <c r="C189" t="n">
-        <v>4261</v>
+        <v>741</v>
       </c>
       <c r="D189" t="n">
         <v>4.292</v>
@@ -31281,7 +31281,7 @@
         <v>33</v>
       </c>
       <c r="C190" t="n">
-        <v>4156</v>
+        <v>723</v>
       </c>
       <c r="D190" t="n">
         <v>4.334</v>
@@ -31303,7 +31303,7 @@
         <v>34</v>
       </c>
       <c r="C191" t="n">
-        <v>4348</v>
+        <v>756</v>
       </c>
       <c r="D191" t="n">
         <v>4.374</v>
@@ -31325,7 +31325,7 @@
         <v>35</v>
       </c>
       <c r="C192" t="n">
-        <v>4302</v>
+        <v>748</v>
       </c>
       <c r="D192" t="n">
         <v>4.413</v>
@@ -31347,7 +31347,7 @@
         <v>36</v>
       </c>
       <c r="C193" t="n">
-        <v>4134</v>
+        <v>719</v>
       </c>
       <c r="D193" t="n">
         <v>4.449</v>
@@ -31369,7 +31369,7 @@
         <v>37</v>
       </c>
       <c r="C194" t="n">
-        <v>4072</v>
+        <v>708</v>
       </c>
       <c r="D194" t="n">
         <v>4.482</v>
@@ -31391,7 +31391,7 @@
         <v>38</v>
       </c>
       <c r="C195" t="n">
-        <v>4186</v>
+        <v>728</v>
       </c>
       <c r="D195" t="n">
         <v>4.512</v>
@@ -31413,7 +31413,7 @@
         <v>39</v>
       </c>
       <c r="C196" t="n">
-        <v>4028</v>
+        <v>700</v>
       </c>
       <c r="D196" t="n">
         <v>4.538</v>
@@ -31435,7 +31435,7 @@
         <v>40</v>
       </c>
       <c r="C197" t="n">
-        <v>3993</v>
+        <v>694</v>
       </c>
       <c r="D197" t="n">
         <v>4.56</v>
@@ -31457,7 +31457,7 @@
         <v>41</v>
       </c>
       <c r="C198" t="n">
-        <v>4037</v>
+        <v>702</v>
       </c>
       <c r="D198" t="n">
         <v>4.577</v>
@@ -31479,7 +31479,7 @@
         <v>42</v>
       </c>
       <c r="C199" t="n">
-        <v>3926</v>
+        <v>683</v>
       </c>
       <c r="D199" t="n">
         <v>4.59</v>
@@ -31501,7 +31501,7 @@
         <v>43</v>
       </c>
       <c r="C200" t="n">
-        <v>3949</v>
+        <v>687</v>
       </c>
       <c r="D200" t="n">
         <v>4.597</v>
@@ -31523,7 +31523,7 @@
         <v>44</v>
       </c>
       <c r="C201" t="n">
-        <v>3874</v>
+        <v>674</v>
       </c>
       <c r="D201" t="n">
         <v>4.6</v>
@@ -31545,7 +31545,7 @@
         <v>45</v>
       </c>
       <c r="C202" t="n">
-        <v>3838</v>
+        <v>667</v>
       </c>
       <c r="D202" t="n">
         <v>4.597</v>
@@ -31567,7 +31567,7 @@
         <v>46</v>
       </c>
       <c r="C203" t="n">
-        <v>3832</v>
+        <v>666</v>
       </c>
       <c r="D203" t="n">
         <v>4.59</v>
@@ -31589,7 +31589,7 @@
         <v>47</v>
       </c>
       <c r="C204" t="n">
-        <v>3758</v>
+        <v>654</v>
       </c>
       <c r="D204" t="n">
         <v>4.577</v>
@@ -31611,7 +31611,7 @@
         <v>48</v>
       </c>
       <c r="C205" t="n">
-        <v>3789</v>
+        <v>659</v>
       </c>
       <c r="D205" t="n">
         <v>4.56</v>
@@ -31633,7 +31633,7 @@
         <v>49</v>
       </c>
       <c r="C206" t="n">
-        <v>3590</v>
+        <v>624</v>
       </c>
       <c r="D206" t="n">
         <v>4.538</v>
@@ -31655,7 +31655,7 @@
         <v>50</v>
       </c>
       <c r="C207" t="n">
-        <v>3653</v>
+        <v>635</v>
       </c>
       <c r="D207" t="n">
         <v>4.512</v>
@@ -31677,7 +31677,7 @@
         <v>51</v>
       </c>
       <c r="C208" t="n">
-        <v>3561</v>
+        <v>619</v>
       </c>
       <c r="D208" t="n">
         <v>4.482</v>
@@ -31699,7 +31699,7 @@
         <v>52</v>
       </c>
       <c r="C209" t="n">
-        <v>3540</v>
+        <v>616</v>
       </c>
       <c r="D209" t="n">
         <v>4.449</v>
@@ -31721,7 +31721,7 @@
         <v>1</v>
       </c>
       <c r="C210" t="n">
-        <v>4574</v>
+        <v>1429</v>
       </c>
       <c r="D210" t="n">
         <v>4.313</v>
@@ -31743,7 +31743,7 @@
         <v>2</v>
       </c>
       <c r="C211" t="n">
-        <v>4643</v>
+        <v>1451</v>
       </c>
       <c r="D211" t="n">
         <v>4.274</v>
@@ -31765,7 +31765,7 @@
         <v>3</v>
       </c>
       <c r="C212" t="n">
-        <v>4761</v>
+        <v>1488</v>
       </c>
       <c r="D212" t="n">
         <v>4.234</v>
@@ -31787,7 +31787,7 @@
         <v>4</v>
       </c>
       <c r="C213" t="n">
-        <v>4604</v>
+        <v>1439</v>
       </c>
       <c r="D213" t="n">
         <v>4.192</v>
@@ -31809,7 +31809,7 @@
         <v>5</v>
       </c>
       <c r="C214" t="n">
-        <v>5117</v>
+        <v>1599</v>
       </c>
       <c r="D214" t="n">
         <v>4.15</v>
@@ -31831,7 +31831,7 @@
         <v>6</v>
       </c>
       <c r="C215" t="n">
-        <v>5493</v>
+        <v>1717</v>
       </c>
       <c r="D215" t="n">
         <v>4.108</v>
@@ -31853,7 +31853,7 @@
         <v>7</v>
       </c>
       <c r="C216" t="n">
-        <v>5922</v>
+        <v>1851</v>
       </c>
       <c r="D216" t="n">
         <v>4.066</v>
@@ -31875,7 +31875,7 @@
         <v>8</v>
       </c>
       <c r="C217" t="n">
-        <v>6041</v>
+        <v>1888</v>
       </c>
       <c r="D217" t="n">
         <v>4.026</v>
@@ -31897,7 +31897,7 @@
         <v>9</v>
       </c>
       <c r="C218" t="n">
-        <v>5999</v>
+        <v>1875</v>
       </c>
       <c r="D218" t="n">
         <v>3.987</v>
@@ -31919,7 +31919,7 @@
         <v>10</v>
       </c>
       <c r="C219" t="n">
-        <v>6592</v>
+        <v>2060</v>
       </c>
       <c r="D219" t="n">
         <v>3.951</v>
@@ -31941,7 +31941,7 @@
         <v>11</v>
       </c>
       <c r="C220" t="n">
-        <v>6957</v>
+        <v>2174</v>
       </c>
       <c r="D220" t="n">
         <v>3.918</v>
@@ -31963,7 +31963,7 @@
         <v>12</v>
       </c>
       <c r="C221" t="n">
-        <v>7406</v>
+        <v>2314</v>
       </c>
       <c r="D221" t="n">
         <v>3.888</v>
@@ -31985,7 +31985,7 @@
         <v>13</v>
       </c>
       <c r="C222" t="n">
-        <v>7459</v>
+        <v>2331</v>
       </c>
       <c r="D222" t="n">
         <v>3.862</v>
@@ -32007,7 +32007,7 @@
         <v>14</v>
       </c>
       <c r="C223" t="n">
-        <v>7775</v>
+        <v>2430</v>
       </c>
       <c r="D223" t="n">
         <v>3.84</v>
@@ -32029,7 +32029,7 @@
         <v>15</v>
       </c>
       <c r="C224" t="n">
-        <v>8032</v>
+        <v>2510</v>
       </c>
       <c r="D224" t="n">
         <v>3.823</v>
@@ -32051,7 +32051,7 @@
         <v>16</v>
       </c>
       <c r="C225" t="n">
-        <v>8139</v>
+        <v>2543</v>
       </c>
       <c r="D225" t="n">
         <v>3.81</v>
@@ -32073,7 +32073,7 @@
         <v>17</v>
       </c>
       <c r="C226" t="n">
-        <v>8285</v>
+        <v>2589</v>
       </c>
       <c r="D226" t="n">
         <v>3.803</v>
@@ -32095,7 +32095,7 @@
         <v>18</v>
       </c>
       <c r="C227" t="n">
-        <v>8193</v>
+        <v>2560</v>
       </c>
       <c r="D227" t="n">
         <v>3.8</v>
@@ -32117,7 +32117,7 @@
         <v>19</v>
       </c>
       <c r="C228" t="n">
-        <v>8361</v>
+        <v>2613</v>
       </c>
       <c r="D228" t="n">
         <v>3.803</v>
@@ -32139,7 +32139,7 @@
         <v>20</v>
       </c>
       <c r="C229" t="n">
-        <v>8172</v>
+        <v>2554</v>
       </c>
       <c r="D229" t="n">
         <v>3.81</v>
@@ -32161,7 +32161,7 @@
         <v>21</v>
       </c>
       <c r="C230" t="n">
-        <v>7847</v>
+        <v>2452</v>
       </c>
       <c r="D230" t="n">
         <v>3.823</v>
@@ -32183,7 +32183,7 @@
         <v>22</v>
       </c>
       <c r="C231" t="n">
-        <v>7914</v>
+        <v>2473</v>
       </c>
       <c r="D231" t="n">
         <v>3.84</v>
@@ -32205,7 +32205,7 @@
         <v>23</v>
       </c>
       <c r="C232" t="n">
-        <v>7501</v>
+        <v>2344</v>
       </c>
       <c r="D232" t="n">
         <v>3.862</v>
@@ -32227,7 +32227,7 @@
         <v>24</v>
       </c>
       <c r="C233" t="n">
-        <v>7325</v>
+        <v>2289</v>
       </c>
       <c r="D233" t="n">
         <v>3.888</v>
@@ -32249,7 +32249,7 @@
         <v>25</v>
       </c>
       <c r="C234" t="n">
-        <v>7146</v>
+        <v>2233</v>
       </c>
       <c r="D234" t="n">
         <v>3.918</v>
@@ -32271,7 +32271,7 @@
         <v>26</v>
       </c>
       <c r="C235" t="n">
-        <v>7241</v>
+        <v>2263</v>
       </c>
       <c r="D235" t="n">
         <v>3.951</v>
@@ -32293,7 +32293,7 @@
         <v>27</v>
       </c>
       <c r="C236" t="n">
-        <v>6789</v>
+        <v>2122</v>
       </c>
       <c r="D236" t="n">
         <v>3.987</v>
@@ -32315,7 +32315,7 @@
         <v>28</v>
       </c>
       <c r="C237" t="n">
-        <v>6552</v>
+        <v>2047</v>
       </c>
       <c r="D237" t="n">
         <v>4.026</v>
@@ -32337,7 +32337,7 @@
         <v>29</v>
       </c>
       <c r="C238" t="n">
-        <v>6164</v>
+        <v>1926</v>
       </c>
       <c r="D238" t="n">
         <v>4.066</v>
@@ -32359,7 +32359,7 @@
         <v>30</v>
       </c>
       <c r="C239" t="n">
-        <v>6354</v>
+        <v>1985</v>
       </c>
       <c r="D239" t="n">
         <v>4.108</v>
@@ -32381,7 +32381,7 @@
         <v>31</v>
       </c>
       <c r="C240" t="n">
-        <v>6085</v>
+        <v>1901</v>
       </c>
       <c r="D240" t="n">
         <v>4.15</v>
@@ -32403,7 +32403,7 @@
         <v>32</v>
       </c>
       <c r="C241" t="n">
-        <v>5950</v>
+        <v>1859</v>
       </c>
       <c r="D241" t="n">
         <v>4.192</v>
@@ -32425,7 +32425,7 @@
         <v>33</v>
       </c>
       <c r="C242" t="n">
-        <v>5735</v>
+        <v>1792</v>
       </c>
       <c r="D242" t="n">
         <v>4.234</v>
@@ -32447,7 +32447,7 @@
         <v>34</v>
       </c>
       <c r="C243" t="n">
-        <v>5804</v>
+        <v>1814</v>
       </c>
       <c r="D243" t="n">
         <v>4.274</v>
@@ -32469,7 +32469,7 @@
         <v>35</v>
       </c>
       <c r="C244" t="n">
-        <v>5568</v>
+        <v>1740</v>
       </c>
       <c r="D244" t="n">
         <v>4.313</v>
@@ -32491,7 +32491,7 @@
         <v>36</v>
       </c>
       <c r="C245" t="n">
-        <v>5502</v>
+        <v>1719</v>
       </c>
       <c r="D245" t="n">
         <v>4.349</v>
@@ -32513,7 +32513,7 @@
         <v>37</v>
       </c>
       <c r="C246" t="n">
-        <v>5710</v>
+        <v>1784</v>
       </c>
       <c r="D246" t="n">
         <v>4.382</v>
@@ -32535,7 +32535,7 @@
         <v>38</v>
       </c>
       <c r="C247" t="n">
-        <v>5426</v>
+        <v>1696</v>
       </c>
       <c r="D247" t="n">
         <v>4.412</v>
@@ -32557,7 +32557,7 @@
         <v>39</v>
       </c>
       <c r="C248" t="n">
-        <v>5442</v>
+        <v>1701</v>
       </c>
       <c r="D248" t="n">
         <v>4.438</v>
@@ -32579,7 +32579,7 @@
         <v>40</v>
       </c>
       <c r="C249" t="n">
-        <v>5590</v>
+        <v>1747</v>
       </c>
       <c r="D249" t="n">
         <v>4.46</v>
@@ -32601,7 +32601,7 @@
         <v>41</v>
       </c>
       <c r="C250" t="n">
-        <v>5580</v>
+        <v>1744</v>
       </c>
       <c r="D250" t="n">
         <v>4.477</v>
@@ -32623,7 +32623,7 @@
         <v>42</v>
       </c>
       <c r="C251" t="n">
-        <v>5162</v>
+        <v>1613</v>
       </c>
       <c r="D251" t="n">
         <v>4.49</v>
@@ -32645,7 +32645,7 @@
         <v>43</v>
       </c>
       <c r="C252" t="n">
-        <v>5225</v>
+        <v>1633</v>
       </c>
       <c r="D252" t="n">
         <v>4.497</v>
@@ -32667,7 +32667,7 @@
         <v>44</v>
       </c>
       <c r="C253" t="n">
-        <v>5157</v>
+        <v>1611</v>
       </c>
       <c r="D253" t="n">
         <v>4.5</v>
@@ -32689,7 +32689,7 @@
         <v>45</v>
       </c>
       <c r="C254" t="n">
-        <v>5136</v>
+        <v>1605</v>
       </c>
       <c r="D254" t="n">
         <v>4.497</v>
@@ -32711,7 +32711,7 @@
         <v>46</v>
       </c>
       <c r="C255" t="n">
-        <v>4810</v>
+        <v>1503</v>
       </c>
       <c r="D255" t="n">
         <v>4.49</v>
@@ -32733,7 +32733,7 @@
         <v>47</v>
       </c>
       <c r="C256" t="n">
-        <v>4865</v>
+        <v>1520</v>
       </c>
       <c r="D256" t="n">
         <v>4.477</v>
@@ -32755,7 +32755,7 @@
         <v>48</v>
       </c>
       <c r="C257" t="n">
-        <v>4940</v>
+        <v>1544</v>
       </c>
       <c r="D257" t="n">
         <v>4.46</v>
@@ -32777,7 +32777,7 @@
         <v>49</v>
       </c>
       <c r="C258" t="n">
-        <v>4821</v>
+        <v>1507</v>
       </c>
       <c r="D258" t="n">
         <v>4.438</v>
@@ -32799,7 +32799,7 @@
         <v>50</v>
       </c>
       <c r="C259" t="n">
-        <v>4670</v>
+        <v>1460</v>
       </c>
       <c r="D259" t="n">
         <v>4.412</v>
@@ -32821,7 +32821,7 @@
         <v>51</v>
       </c>
       <c r="C260" t="n">
-        <v>4595</v>
+        <v>1436</v>
       </c>
       <c r="D260" t="n">
         <v>4.382</v>
@@ -32843,7 +32843,7 @@
         <v>52</v>
       </c>
       <c r="C261" t="n">
-        <v>4509</v>
+        <v>1409</v>
       </c>
       <c r="D261" t="n">
         <v>4.349</v>
@@ -32920,10 +32920,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24000</v>
+        <v>6144</v>
       </c>
       <c r="E2" t="n">
-        <v>1500</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3">
@@ -32943,10 +32943,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32000</v>
+        <v>8192</v>
       </c>
       <c r="E3" t="n">
-        <v>1500</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4">
@@ -32966,10 +32966,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14000</v>
+        <v>3584</v>
       </c>
       <c r="E4" t="n">
-        <v>1000</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -33461,17 +33461,17 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1500</v>
+        <v>384</v>
       </c>
       <c r="J2" t="n">
-        <v>8000</v>
+        <v>2048</v>
       </c>
       <c r="K2" t="n">
         <v>8</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>1500</v>
+        <v>384</v>
       </c>
       <c r="N2" t="inlineStr"/>
     </row>
@@ -33505,17 +33505,17 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1500</v>
+        <v>384</v>
       </c>
       <c r="J3" t="n">
-        <v>8000</v>
+        <v>2048</v>
       </c>
       <c r="K3" t="n">
         <v>8</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>1500</v>
+        <v>384</v>
       </c>
       <c r="N3" t="inlineStr"/>
     </row>
@@ -33550,7 +33550,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2000</v>
+        <v>512</v>
       </c>
       <c r="K4" t="n">
         <v>10</v>
@@ -33592,7 +33592,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4000</v>
+        <v>1024</v>
       </c>
       <c r="K5" t="n">
         <v>6</v>
@@ -33634,7 +33634,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2000</v>
+        <v>512</v>
       </c>
       <c r="K6" t="n">
         <v>6</v>
@@ -33676,7 +33676,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3000</v>
+        <v>768</v>
       </c>
       <c r="K7" t="n">
         <v>6</v>
@@ -33718,7 +33718,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2000</v>
+        <v>512</v>
       </c>
       <c r="K8" t="n">
         <v>12</v>
@@ -33762,7 +33762,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
         <v>100</v>
@@ -33801,17 +33801,17 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
       <c r="J10" t="n">
-        <v>3000</v>
+        <v>768</v>
       </c>
       <c r="K10" t="n">
         <v>15</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
       <c r="N10" t="inlineStr"/>
     </row>
@@ -33845,10 +33845,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3000</v>
+        <v>768</v>
       </c>
       <c r="J11" t="n">
-        <v>6000</v>
+        <v>1536</v>
       </c>
       <c r="K11" t="n">
         <v>12</v>
@@ -33857,7 +33857,7 @@
         <v>15000</v>
       </c>
       <c r="M11" t="n">
-        <v>3000</v>
+        <v>768</v>
       </c>
       <c r="N11" t="inlineStr"/>
     </row>
@@ -33894,7 +33894,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>600</v>
+        <v>154</v>
       </c>
       <c r="K12" t="n">
         <v>15</v>
@@ -33937,10 +33937,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>500</v>
+        <v>128</v>
       </c>
       <c r="J13" t="n">
-        <v>2000</v>
+        <v>512</v>
       </c>
       <c r="K13" t="n">
         <v>10</v>
@@ -33949,7 +33949,7 @@
         <v>20000</v>
       </c>
       <c r="M13" t="n">
-        <v>500</v>
+        <v>128</v>
       </c>
       <c r="N13" t="inlineStr"/>
     </row>
@@ -33986,7 +33986,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>800</v>
+        <v>205</v>
       </c>
       <c r="K14" t="n">
         <v>15</v>
